--- a/output/2026-09-21/enriched_analysis.xlsx
+++ b/output/2026-09-21/enriched_analysis.xlsx
@@ -7573,12 +7573,12 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>VIVIANA</t>
+          <t>NPST</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>VIVIANA POWER TECH LIMITED</t>
+          <t>NETWORK PEOPLE SERVICES TECHNOLOGIES LIMITED</t>
         </is>
       </c>
       <c r="C31" t="n">
@@ -7590,185 +7590,187 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>9</v>
+        <v>2</v>
       </c>
       <c r="F31" t="n">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="G31" t="n">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="H31" t="n">
-        <v>0</v>
+        <v>-16</v>
       </c>
       <c r="I31" t="n">
-        <v>718.8</v>
+        <v>1828.5</v>
       </c>
       <c r="J31" t="n">
-        <v>799.47</v>
+        <v>789.9400000000001</v>
       </c>
       <c r="K31" t="n">
-        <v>-10.1</v>
+        <v>131.5</v>
       </c>
       <c r="L31" t="n">
-        <v>73.2</v>
+        <v>67.55</v>
       </c>
       <c r="M31" t="n">
-        <v>1.42</v>
+        <v>12.76</v>
       </c>
       <c r="N31" t="n">
-        <v>14160174</v>
+        <v>127606073</v>
       </c>
       <c r="O31" t="n">
-        <v>0</v>
+        <v>130033072</v>
       </c>
       <c r="P31" t="n">
-        <v>14160174</v>
+        <v>-2426999</v>
       </c>
       <c r="Q31" t="n">
-        <v>0</v>
+        <v>101.9</v>
       </c>
       <c r="R31" t="inlineStr">
         <is>
-          <t>Net Buying</t>
+          <t>Net Selling</t>
         </is>
       </c>
       <c r="S31" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T31" t="n">
+        <v>6</v>
+      </c>
+      <c r="U31" t="inlineStr">
+        <is>
+          <t>25-06-2026</t>
+        </is>
+      </c>
+      <c r="V31" t="n">
+        <v>0</v>
+      </c>
+      <c r="W31" t="n">
+        <v>3815</v>
+      </c>
+      <c r="X31" t="n">
+        <v>85.90000000000001</v>
+      </c>
+      <c r="Y31" t="n">
+        <v>42</v>
+      </c>
+      <c r="Z31" t="n">
+        <v>13</v>
+      </c>
+      <c r="AA31" t="n">
+        <v>22</v>
+      </c>
+      <c r="AB31" t="n">
+        <v>5.05</v>
+      </c>
+      <c r="AC31" t="n">
+        <v>19.8</v>
+      </c>
+      <c r="AD31" t="n">
+        <v>0.03</v>
+      </c>
+      <c r="AE31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF31" t="n">
+        <v>27</v>
+      </c>
+      <c r="AG31" t="n">
+        <v>1614.67</v>
+      </c>
+      <c r="AH31" t="n">
+        <v>1381.2</v>
+      </c>
+      <c r="AI31" t="n">
+        <v>108.1</v>
+      </c>
+      <c r="AJ31" t="n">
+        <v>789.9446136512771</v>
+      </c>
+      <c r="AK31" t="n">
+        <v>131.5</v>
+      </c>
+      <c r="AL31" t="inlineStr">
+        <is>
+          <t>Stale</t>
+        </is>
+      </c>
+      <c r="AM31" t="inlineStr">
+        <is>
+          <t>Stale Accumulation</t>
+        </is>
+      </c>
+      <c r="AN31" t="inlineStr">
+        <is>
+          <t>Late — Poor Entry</t>
+        </is>
+      </c>
+      <c r="AO31" t="inlineStr">
+        <is>
+          <t>25-06-2026</t>
+        </is>
+      </c>
+      <c r="AP31" t="inlineStr">
+        <is>
+          <t>25-06-2026</t>
+        </is>
+      </c>
+      <c r="AQ31" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR31" t="n">
+        <v>88</v>
+      </c>
+      <c r="AS31" t="n">
+        <v>88</v>
+      </c>
+      <c r="AT31" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU31" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV31" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW31" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX31" t="n">
+        <v>12</v>
+      </c>
+      <c r="AY31" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ31" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA31" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB31" t="n">
+        <v>0</v>
+      </c>
+      <c r="BC31" t="n">
+        <v>255212146</v>
+      </c>
+      <c r="BD31" t="n">
+        <v>0</v>
+      </c>
+      <c r="BE31" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF31" t="n">
+        <v>0</v>
+      </c>
+      <c r="BG31" t="n">
+        <v>0</v>
+      </c>
+      <c r="BH31" t="n">
         <v>4</v>
       </c>
-      <c r="U31" t="inlineStr">
-        <is>
-          <t>17-09-2026</t>
-        </is>
-      </c>
-      <c r="V31" t="n">
-        <v>0.195</v>
-      </c>
-      <c r="W31" t="n">
-        <v>728</v>
-      </c>
-      <c r="X31" t="n">
-        <v>13.2</v>
-      </c>
-      <c r="Y31" t="n">
-        <v>185</v>
-      </c>
-      <c r="Z31" t="n">
-        <v>11.55</v>
-      </c>
-      <c r="AA31" t="n">
-        <v>204</v>
-      </c>
-      <c r="AB31" t="n">
-        <v>6.84</v>
-      </c>
-      <c r="AC31" t="n">
-        <v>50.7</v>
-      </c>
-      <c r="AD31" t="n">
-        <v>0.8100000000000001</v>
-      </c>
-      <c r="AE31" t="b">
-        <v>1</v>
-      </c>
-      <c r="AF31" t="n">
-        <v>16.07</v>
-      </c>
-      <c r="AG31" t="n">
-        <v>729.78</v>
-      </c>
-      <c r="AH31" t="inlineStr"/>
-      <c r="AI31" t="n">
-        <v>-20.9</v>
-      </c>
-      <c r="AJ31" t="n">
-        <v>799.4678184281843</v>
-      </c>
-      <c r="AK31" t="n">
-        <v>-10.1</v>
-      </c>
-      <c r="AL31" t="inlineStr">
-        <is>
-          <t>Fresh</t>
-        </is>
-      </c>
-      <c r="AM31" t="inlineStr">
-        <is>
-          <t>Confirmed Accumulation</t>
-        </is>
-      </c>
-      <c r="AN31" t="inlineStr">
-        <is>
-          <t>Confirmed Accumulation</t>
-        </is>
-      </c>
-      <c r="AO31" t="inlineStr">
-        <is>
-          <t>19-06-2026</t>
-        </is>
-      </c>
-      <c r="AP31" t="inlineStr">
-        <is>
-          <t>17-09-2026</t>
-        </is>
-      </c>
-      <c r="AQ31" t="n">
-        <v>90</v>
-      </c>
-      <c r="AR31" t="n">
-        <v>94</v>
-      </c>
-      <c r="AS31" t="n">
-        <v>4</v>
-      </c>
-      <c r="AT31" t="n">
-        <v>1</v>
-      </c>
-      <c r="AU31" t="n">
-        <v>1</v>
-      </c>
-      <c r="AV31" t="n">
-        <v>1</v>
-      </c>
-      <c r="AW31" t="n">
-        <v>1</v>
-      </c>
-      <c r="AX31" t="n">
-        <v>2</v>
-      </c>
-      <c r="AY31" t="n">
-        <v>1751854</v>
-      </c>
-      <c r="AZ31" t="n">
-        <v>1751854</v>
-      </c>
-      <c r="BA31" t="n">
-        <v>1751854</v>
-      </c>
-      <c r="BB31" t="n">
-        <v>1751854</v>
-      </c>
-      <c r="BC31" t="n">
-        <v>5375657</v>
-      </c>
-      <c r="BD31" t="n">
-        <v>0</v>
-      </c>
-      <c r="BE31" t="n">
-        <v>0</v>
-      </c>
-      <c r="BF31" t="n">
-        <v>0</v>
-      </c>
-      <c r="BG31" t="n">
-        <v>0</v>
-      </c>
-      <c r="BH31" t="n">
-        <v>0</v>
-      </c>
       <c r="BI31" t="n">
         <v>0</v>
       </c>
@@ -7782,22 +7784,22 @@
         <v>0</v>
       </c>
       <c r="BM31" t="n">
-        <v>0</v>
+        <v>260066144</v>
       </c>
       <c r="BN31" t="n">
-        <v>1751854</v>
+        <v>0</v>
       </c>
       <c r="BO31" t="n">
-        <v>1751854</v>
+        <v>0</v>
       </c>
       <c r="BP31" t="n">
         <v>2</v>
       </c>
       <c r="BQ31" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="BR31" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="32">
@@ -8035,16 +8037,16 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>NPST</t>
+          <t>AMANTA</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>NETWORK PEOPLE SERVICES TECHNOLOGIES LIMITED</t>
+          <t>Amanta Healthcare Limited</t>
         </is>
       </c>
       <c r="C33" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -8052,107 +8054,107 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F33" t="n">
-        <v>17</v>
+        <v>5</v>
       </c>
       <c r="G33" t="n">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="H33" t="n">
-        <v>-16</v>
+        <v>0</v>
       </c>
       <c r="I33" t="n">
-        <v>1828.5</v>
+        <v>189.95</v>
       </c>
       <c r="J33" t="n">
-        <v>789.9400000000001</v>
+        <v>149.98</v>
       </c>
       <c r="K33" t="n">
-        <v>131.5</v>
+        <v>26.7</v>
       </c>
       <c r="L33" t="n">
-        <v>67.55</v>
+        <v>63.56</v>
       </c>
       <c r="M33" t="n">
-        <v>12.76</v>
+        <v>0.24</v>
       </c>
       <c r="N33" t="n">
-        <v>127606073</v>
+        <v>2429680</v>
       </c>
       <c r="O33" t="n">
-        <v>130033072</v>
+        <v>0</v>
       </c>
       <c r="P33" t="n">
-        <v>-2426999</v>
+        <v>2429680</v>
       </c>
       <c r="Q33" t="n">
-        <v>101.9</v>
+        <v>0</v>
       </c>
       <c r="R33" t="inlineStr">
         <is>
-          <t>Net Selling</t>
+          <t>Net Buying</t>
         </is>
       </c>
       <c r="S33" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T33" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="U33" t="inlineStr">
         <is>
-          <t>25-06-2026</t>
+          <t>18-06-2026</t>
         </is>
       </c>
       <c r="V33" t="n">
-        <v>0</v>
+        <v>0.033</v>
       </c>
       <c r="W33" t="n">
-        <v>3815</v>
+        <v>738</v>
       </c>
       <c r="X33" t="n">
-        <v>85.90000000000001</v>
+        <v>48.1</v>
       </c>
       <c r="Y33" t="n">
-        <v>42</v>
+        <v>7</v>
       </c>
       <c r="Z33" t="n">
-        <v>13</v>
+        <v>14.54</v>
       </c>
       <c r="AA33" t="n">
-        <v>22</v>
+        <v>-4</v>
       </c>
       <c r="AB33" t="n">
-        <v>5.05</v>
+        <v>0.85</v>
       </c>
       <c r="AC33" t="n">
-        <v>19.8</v>
+        <v>11.6</v>
       </c>
       <c r="AD33" t="n">
-        <v>0.03</v>
+        <v>1.11</v>
       </c>
       <c r="AE33" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AF33" t="n">
-        <v>27</v>
+        <v>21.13</v>
       </c>
       <c r="AG33" t="n">
-        <v>1614.67</v>
+        <v>177.79</v>
       </c>
       <c r="AH33" t="n">
-        <v>1381.2</v>
+        <v>133.78</v>
       </c>
       <c r="AI33" t="n">
-        <v>108.1</v>
+        <v>94.90000000000001</v>
       </c>
       <c r="AJ33" t="n">
-        <v>789.9446136512771</v>
+        <v>149.9802469135803</v>
       </c>
       <c r="AK33" t="n">
-        <v>131.5</v>
+        <v>26.7</v>
       </c>
       <c r="AL33" t="inlineStr">
         <is>
@@ -8171,22 +8173,22 @@
       </c>
       <c r="AO33" t="inlineStr">
         <is>
-          <t>25-06-2026</t>
+          <t>18-06-2026</t>
         </is>
       </c>
       <c r="AP33" t="inlineStr">
         <is>
-          <t>25-06-2026</t>
+          <t>18-06-2026</t>
         </is>
       </c>
       <c r="AQ33" t="n">
         <v>0</v>
       </c>
       <c r="AR33" t="n">
-        <v>88</v>
+        <v>95</v>
       </c>
       <c r="AS33" t="n">
-        <v>88</v>
+        <v>95</v>
       </c>
       <c r="AT33" t="n">
         <v>0</v>
@@ -8201,7 +8203,7 @@
         <v>0</v>
       </c>
       <c r="AX33" t="n">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="AY33" t="n">
         <v>0</v>
@@ -8216,7 +8218,7 @@
         <v>0</v>
       </c>
       <c r="BC33" t="n">
-        <v>255212146</v>
+        <v>0</v>
       </c>
       <c r="BD33" t="n">
         <v>0</v>
@@ -8231,7 +8233,7 @@
         <v>0</v>
       </c>
       <c r="BH33" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="BI33" t="n">
         <v>0</v>
@@ -8246,7 +8248,7 @@
         <v>0</v>
       </c>
       <c r="BM33" t="n">
-        <v>260066144</v>
+        <v>0</v>
       </c>
       <c r="BN33" t="n">
         <v>0</v>
@@ -8255,10 +8257,10 @@
         <v>0</v>
       </c>
       <c r="BP33" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="BQ33" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="BR33" t="n">
         <v>0</v>
@@ -8727,16 +8729,16 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>AMANTA</t>
+          <t>PLASTIBLEN</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>Amanta Healthcare Limited</t>
+          <t>PLASTIBLENDS INDIA LIMITED</t>
         </is>
       </c>
       <c r="C36" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -8744,107 +8746,107 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F36" t="n">
-        <v>5</v>
+        <v>18</v>
       </c>
       <c r="G36" t="n">
         <v>21</v>
       </c>
       <c r="H36" t="n">
-        <v>0</v>
+        <v>-15</v>
       </c>
       <c r="I36" t="n">
-        <v>189.95</v>
+        <v>186.63</v>
       </c>
       <c r="J36" t="n">
-        <v>149.98</v>
+        <v>175.84</v>
       </c>
       <c r="K36" t="n">
-        <v>26.7</v>
+        <v>6.1</v>
       </c>
       <c r="L36" t="n">
-        <v>63.56</v>
+        <v>64.20999999999999</v>
       </c>
       <c r="M36" t="n">
-        <v>0.24</v>
+        <v>7.95</v>
       </c>
       <c r="N36" t="n">
-        <v>2429680</v>
+        <v>79549544</v>
       </c>
       <c r="O36" t="n">
-        <v>0</v>
+        <v>110497109</v>
       </c>
       <c r="P36" t="n">
-        <v>2429680</v>
+        <v>-30947565</v>
       </c>
       <c r="Q36" t="n">
-        <v>0</v>
+        <v>138.9</v>
       </c>
       <c r="R36" t="inlineStr">
         <is>
-          <t>Net Buying</t>
+          <t>Net Selling</t>
         </is>
       </c>
       <c r="S36" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T36" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="U36" t="inlineStr">
         <is>
-          <t>18-06-2026</t>
+          <t>25-06-2026</t>
         </is>
       </c>
       <c r="V36" t="n">
-        <v>0.033</v>
+        <v>0</v>
       </c>
       <c r="W36" t="n">
-        <v>738</v>
+        <v>485</v>
       </c>
       <c r="X36" t="n">
-        <v>48.1</v>
+        <v>11.4</v>
       </c>
       <c r="Y36" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="Z36" t="n">
-        <v>14.54</v>
+        <v>22</v>
       </c>
       <c r="AA36" t="n">
-        <v>-4</v>
+        <v>36</v>
       </c>
       <c r="AB36" t="n">
-        <v>0.85</v>
+        <v>5.75</v>
       </c>
       <c r="AC36" t="n">
-        <v>11.6</v>
+        <v>10.7</v>
       </c>
       <c r="AD36" t="n">
-        <v>1.11</v>
+        <v>0.05</v>
       </c>
       <c r="AE36" t="b">
         <v>1</v>
       </c>
       <c r="AF36" t="n">
-        <v>21.13</v>
+        <v>10</v>
       </c>
       <c r="AG36" t="n">
-        <v>177.79</v>
+        <v>191.6</v>
       </c>
       <c r="AH36" t="n">
-        <v>133.78</v>
+        <v>166.91</v>
       </c>
       <c r="AI36" t="n">
-        <v>94.90000000000001</v>
+        <v>41.6</v>
       </c>
       <c r="AJ36" t="n">
-        <v>149.9802469135803</v>
+        <v>175.8389566755084</v>
       </c>
       <c r="AK36" t="n">
-        <v>26.7</v>
+        <v>6.1</v>
       </c>
       <c r="AL36" t="inlineStr">
         <is>
@@ -8863,22 +8865,22 @@
       </c>
       <c r="AO36" t="inlineStr">
         <is>
-          <t>18-06-2026</t>
+          <t>25-06-2026</t>
         </is>
       </c>
       <c r="AP36" t="inlineStr">
         <is>
-          <t>18-06-2026</t>
+          <t>25-06-2026</t>
         </is>
       </c>
       <c r="AQ36" t="n">
         <v>0</v>
       </c>
       <c r="AR36" t="n">
-        <v>95</v>
+        <v>88</v>
       </c>
       <c r="AS36" t="n">
-        <v>95</v>
+        <v>88</v>
       </c>
       <c r="AT36" t="n">
         <v>0</v>
@@ -8893,7 +8895,7 @@
         <v>0</v>
       </c>
       <c r="AX36" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AY36" t="n">
         <v>0</v>
@@ -8908,7 +8910,7 @@
         <v>0</v>
       </c>
       <c r="BC36" t="n">
-        <v>0</v>
+        <v>79549544</v>
       </c>
       <c r="BD36" t="n">
         <v>0</v>
@@ -8923,7 +8925,7 @@
         <v>0</v>
       </c>
       <c r="BH36" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="BI36" t="n">
         <v>0</v>
@@ -8938,7 +8940,7 @@
         <v>0</v>
       </c>
       <c r="BM36" t="n">
-        <v>0</v>
+        <v>110497109</v>
       </c>
       <c r="BN36" t="n">
         <v>0</v>
@@ -8947,10 +8949,10 @@
         <v>0</v>
       </c>
       <c r="BP36" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="BQ36" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="BR36" t="n">
         <v>0</v>
@@ -8959,12 +8961,12 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>OMPOWER</t>
+          <t>VSTL</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>Om Power Transmission Limited</t>
+          <t>VIBHOR STEEL TUBES LIMITED</t>
         </is>
       </c>
       <c r="C37" t="n">
@@ -8979,136 +8981,138 @@
         <v>5</v>
       </c>
       <c r="F37" t="n">
+        <v>9</v>
+      </c>
+      <c r="G37" t="n">
+        <v>13</v>
+      </c>
+      <c r="H37" t="n">
+        <v>-1</v>
+      </c>
+      <c r="I37" t="n">
+        <v>113.54</v>
+      </c>
+      <c r="J37" t="n">
+        <v>111.01</v>
+      </c>
+      <c r="K37" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="L37" t="n">
+        <v>73.48</v>
+      </c>
+      <c r="M37" t="n">
+        <v>0.45</v>
+      </c>
+      <c r="N37" t="n">
+        <v>4484713</v>
+      </c>
+      <c r="O37" t="n">
+        <v>0</v>
+      </c>
+      <c r="P37" t="n">
+        <v>4484713</v>
+      </c>
+      <c r="Q37" t="n">
+        <v>0</v>
+      </c>
+      <c r="R37" t="inlineStr">
+        <is>
+          <t>Net Buying</t>
+        </is>
+      </c>
+      <c r="S37" t="b">
+        <v>0</v>
+      </c>
+      <c r="T37" t="n">
+        <v>8</v>
+      </c>
+      <c r="U37" t="inlineStr">
+        <is>
+          <t>03-09-2026</t>
+        </is>
+      </c>
+      <c r="V37" t="n">
+        <v>0.209</v>
+      </c>
+      <c r="W37" t="n">
+        <v>215</v>
+      </c>
+      <c r="X37" t="n">
+        <v>25.6</v>
+      </c>
+      <c r="Y37" t="n">
+        <v>21</v>
+      </c>
+      <c r="Z37" t="n">
+        <v>12.07</v>
+      </c>
+      <c r="AA37" t="n">
+        <v>-29</v>
+      </c>
+      <c r="AB37" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="AC37" t="n">
+        <v>7.92</v>
+      </c>
+      <c r="AD37" t="n">
+        <v>0.98</v>
+      </c>
+      <c r="AE37" t="b">
+        <v>1</v>
+      </c>
+      <c r="AF37" t="n">
+        <v>4.11</v>
+      </c>
+      <c r="AG37" t="n">
+        <v>112.01</v>
+      </c>
+      <c r="AH37" t="n">
+        <v>118.75</v>
+      </c>
+      <c r="AI37" t="n">
+        <v>5.2</v>
+      </c>
+      <c r="AJ37" t="n">
+        <v>111.3431590909091</v>
+      </c>
+      <c r="AK37" t="n">
+        <v>2</v>
+      </c>
+      <c r="AL37" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="AM37" t="inlineStr">
+        <is>
+          <t>Confirmed Accumulation</t>
+        </is>
+      </c>
+      <c r="AN37" t="inlineStr">
+        <is>
+          <t>Confirmed Accumulation</t>
+        </is>
+      </c>
+      <c r="AO37" t="inlineStr">
+        <is>
+          <t>17-08-2026</t>
+        </is>
+      </c>
+      <c r="AP37" t="inlineStr">
+        <is>
+          <t>03-09-2026</t>
+        </is>
+      </c>
+      <c r="AQ37" t="n">
         <v>17</v>
       </c>
-      <c r="G37" t="n">
-        <v>4</v>
-      </c>
-      <c r="H37" t="n">
-        <v>0</v>
-      </c>
-      <c r="I37" t="n">
-        <v>172.37</v>
-      </c>
-      <c r="J37" t="n">
-        <v>182.69</v>
-      </c>
-      <c r="K37" t="n">
-        <v>-5.6</v>
-      </c>
-      <c r="L37" t="n">
-        <v>69.05</v>
-      </c>
-      <c r="M37" t="n">
-        <v>0.74</v>
-      </c>
-      <c r="N37" t="n">
-        <v>7447179</v>
-      </c>
-      <c r="O37" t="n">
-        <v>0</v>
-      </c>
-      <c r="P37" t="n">
-        <v>7447179</v>
-      </c>
-      <c r="Q37" t="n">
-        <v>0</v>
-      </c>
-      <c r="R37" t="inlineStr">
-        <is>
-          <t>Net Buying</t>
-        </is>
-      </c>
-      <c r="S37" t="b">
-        <v>0</v>
-      </c>
-      <c r="T37" t="n">
-        <v>3</v>
-      </c>
-      <c r="U37" t="inlineStr">
-        <is>
-          <t>24-06-2026</t>
-        </is>
-      </c>
-      <c r="V37" t="n">
-        <v>0.126</v>
-      </c>
-      <c r="W37" t="n">
-        <v>590</v>
-      </c>
-      <c r="X37" t="n">
-        <v>14</v>
-      </c>
-      <c r="Y37" t="n">
-        <v>61</v>
-      </c>
-      <c r="Z37" t="n">
-        <v>15</v>
-      </c>
-      <c r="AA37" t="n">
-        <v>82</v>
-      </c>
-      <c r="AB37" t="n">
-        <v>3.07</v>
-      </c>
-      <c r="AC37" t="n">
-        <v>42.7</v>
-      </c>
-      <c r="AD37" t="n">
-        <v>0.35</v>
-      </c>
-      <c r="AE37" t="b">
-        <v>0</v>
-      </c>
-      <c r="AF37" t="n">
-        <v>12</v>
-      </c>
-      <c r="AG37" t="n">
-        <v>169.28</v>
-      </c>
-      <c r="AH37" t="inlineStr"/>
-      <c r="AI37" t="n">
-        <v>-10.9</v>
-      </c>
-      <c r="AJ37" t="n">
-        <v>182.6945759634963</v>
-      </c>
-      <c r="AK37" t="n">
-        <v>-5.7</v>
-      </c>
-      <c r="AL37" t="inlineStr">
-        <is>
-          <t>Stale</t>
-        </is>
-      </c>
-      <c r="AM37" t="inlineStr">
-        <is>
-          <t>Stale Accumulation</t>
-        </is>
-      </c>
-      <c r="AN37" t="inlineStr">
-        <is>
-          <t>Late — Poor Entry</t>
-        </is>
-      </c>
-      <c r="AO37" t="inlineStr">
-        <is>
-          <t>24-06-2026</t>
-        </is>
-      </c>
-      <c r="AP37" t="inlineStr">
-        <is>
-          <t>24-06-2026</t>
-        </is>
-      </c>
-      <c r="AQ37" t="n">
-        <v>0</v>
-      </c>
       <c r="AR37" t="n">
-        <v>89</v>
+        <v>35</v>
       </c>
       <c r="AS37" t="n">
-        <v>89</v>
+        <v>18</v>
       </c>
       <c r="AT37" t="n">
         <v>0</v>
@@ -9117,13 +9121,13 @@
         <v>0</v>
       </c>
       <c r="AV37" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="AW37" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="AX37" t="n">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="AY37" t="n">
         <v>0</v>
@@ -9132,13 +9136,13 @@
         <v>0</v>
       </c>
       <c r="BA37" t="n">
-        <v>0</v>
+        <v>3936339</v>
       </c>
       <c r="BB37" t="n">
-        <v>0</v>
+        <v>4899099</v>
       </c>
       <c r="BC37" t="n">
-        <v>7447179</v>
+        <v>4899099</v>
       </c>
       <c r="BD37" t="n">
         <v>0</v>
@@ -9174,10 +9178,10 @@
         <v>0</v>
       </c>
       <c r="BO37" t="n">
-        <v>0</v>
+        <v>3936339</v>
       </c>
       <c r="BP37" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="BQ37" t="n">
         <v>0</v>
@@ -9189,12 +9193,12 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>VSTL</t>
+          <t>OMPOWER</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>VIBHOR STEEL TUBES LIMITED</t>
+          <t>Om Power Transmission Limited</t>
         </is>
       </c>
       <c r="C38" t="n">
@@ -9209,37 +9213,37 @@
         <v>5</v>
       </c>
       <c r="F38" t="n">
-        <v>9</v>
+        <v>17</v>
       </c>
       <c r="G38" t="n">
-        <v>13</v>
+        <v>4</v>
       </c>
       <c r="H38" t="n">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="I38" t="n">
-        <v>113.54</v>
+        <v>172.37</v>
       </c>
       <c r="J38" t="n">
-        <v>111.01</v>
+        <v>182.69</v>
       </c>
       <c r="K38" t="n">
-        <v>2.3</v>
+        <v>-5.6</v>
       </c>
       <c r="L38" t="n">
-        <v>73.48</v>
+        <v>69.05</v>
       </c>
       <c r="M38" t="n">
-        <v>0.45</v>
+        <v>0.74</v>
       </c>
       <c r="N38" t="n">
-        <v>4484713</v>
+        <v>7447179</v>
       </c>
       <c r="O38" t="n">
         <v>0</v>
       </c>
       <c r="P38" t="n">
-        <v>4484713</v>
+        <v>7447179</v>
       </c>
       <c r="Q38" t="n">
         <v>0</v>
@@ -9253,94 +9257,92 @@
         <v>0</v>
       </c>
       <c r="T38" t="n">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="U38" t="inlineStr">
         <is>
-          <t>03-09-2026</t>
+          <t>24-06-2026</t>
         </is>
       </c>
       <c r="V38" t="n">
-        <v>0.209</v>
+        <v>0.126</v>
       </c>
       <c r="W38" t="n">
-        <v>215</v>
+        <v>590</v>
       </c>
       <c r="X38" t="n">
-        <v>25.6</v>
+        <v>14</v>
       </c>
       <c r="Y38" t="n">
-        <v>21</v>
+        <v>61</v>
       </c>
       <c r="Z38" t="n">
-        <v>12.07</v>
+        <v>15</v>
       </c>
       <c r="AA38" t="n">
-        <v>-29</v>
+        <v>82</v>
       </c>
       <c r="AB38" t="n">
-        <v>1.02</v>
+        <v>3.07</v>
       </c>
       <c r="AC38" t="n">
-        <v>7.92</v>
+        <v>42.7</v>
       </c>
       <c r="AD38" t="n">
-        <v>0.98</v>
+        <v>0.35</v>
       </c>
       <c r="AE38" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AF38" t="n">
-        <v>4.11</v>
+        <v>12</v>
       </c>
       <c r="AG38" t="n">
-        <v>112.01</v>
-      </c>
-      <c r="AH38" t="n">
-        <v>118.75</v>
-      </c>
+        <v>169.28</v>
+      </c>
+      <c r="AH38" t="inlineStr"/>
       <c r="AI38" t="n">
-        <v>5.2</v>
+        <v>-10.9</v>
       </c>
       <c r="AJ38" t="n">
-        <v>111.3431590909091</v>
+        <v>182.6945759634963</v>
       </c>
       <c r="AK38" t="n">
-        <v>2</v>
+        <v>-5.7</v>
       </c>
       <c r="AL38" t="inlineStr">
         <is>
-          <t>Active</t>
+          <t>Stale</t>
         </is>
       </c>
       <c r="AM38" t="inlineStr">
         <is>
-          <t>Confirmed Accumulation</t>
+          <t>Stale Accumulation</t>
         </is>
       </c>
       <c r="AN38" t="inlineStr">
         <is>
-          <t>Confirmed Accumulation</t>
+          <t>Late — Poor Entry</t>
         </is>
       </c>
       <c r="AO38" t="inlineStr">
         <is>
-          <t>17-08-2026</t>
+          <t>24-06-2026</t>
         </is>
       </c>
       <c r="AP38" t="inlineStr">
         <is>
-          <t>03-09-2026</t>
+          <t>24-06-2026</t>
         </is>
       </c>
       <c r="AQ38" t="n">
-        <v>17</v>
+        <v>0</v>
       </c>
       <c r="AR38" t="n">
-        <v>35</v>
+        <v>89</v>
       </c>
       <c r="AS38" t="n">
-        <v>18</v>
+        <v>89</v>
       </c>
       <c r="AT38" t="n">
         <v>0</v>
@@ -9349,13 +9351,13 @@
         <v>0</v>
       </c>
       <c r="AV38" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="AW38" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="AX38" t="n">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="AY38" t="n">
         <v>0</v>
@@ -9364,13 +9366,13 @@
         <v>0</v>
       </c>
       <c r="BA38" t="n">
-        <v>3936339</v>
+        <v>0</v>
       </c>
       <c r="BB38" t="n">
-        <v>4899099</v>
+        <v>0</v>
       </c>
       <c r="BC38" t="n">
-        <v>4899099</v>
+        <v>7447179</v>
       </c>
       <c r="BD38" t="n">
         <v>0</v>
@@ -9406,10 +9408,10 @@
         <v>0</v>
       </c>
       <c r="BO38" t="n">
-        <v>3936339</v>
+        <v>0</v>
       </c>
       <c r="BP38" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="BQ38" t="n">
         <v>0</v>
@@ -9421,16 +9423,16 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>PLASTIBLEN</t>
+          <t>HEXAGON</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>PLASTIBLENDS INDIA LIMITED</t>
+          <t>HEXAGON NUTRITION LIMITED</t>
         </is>
       </c>
       <c r="C39" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -9438,171 +9440,163 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="F39" t="n">
-        <v>18</v>
+        <v>8</v>
       </c>
       <c r="G39" t="n">
-        <v>21</v>
+        <v>9</v>
       </c>
       <c r="H39" t="n">
-        <v>-15</v>
+        <v>0</v>
       </c>
       <c r="I39" t="n">
-        <v>186.63</v>
+        <v>66.26000000000001</v>
       </c>
       <c r="J39" t="n">
-        <v>175.84</v>
+        <v>64.48999999999999</v>
       </c>
       <c r="K39" t="n">
-        <v>6.1</v>
+        <v>2.7</v>
       </c>
       <c r="L39" t="n">
-        <v>64.20999999999999</v>
+        <v>64.29000000000001</v>
       </c>
       <c r="M39" t="n">
-        <v>7.95</v>
+        <v>0.57</v>
       </c>
       <c r="N39" t="n">
-        <v>79549544</v>
+        <v>5656038</v>
       </c>
       <c r="O39" t="n">
-        <v>110497109</v>
+        <v>0</v>
       </c>
       <c r="P39" t="n">
-        <v>-30947565</v>
+        <v>5656038</v>
       </c>
       <c r="Q39" t="n">
-        <v>138.9</v>
+        <v>0</v>
       </c>
       <c r="R39" t="inlineStr">
         <is>
-          <t>Net Selling</t>
+          <t>Net Buying</t>
         </is>
       </c>
       <c r="S39" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T39" t="n">
-        <v>2</v>
+        <v>9</v>
       </c>
       <c r="U39" t="inlineStr">
         <is>
-          <t>25-06-2026</t>
+          <t>18-09-2026</t>
         </is>
       </c>
       <c r="V39" t="n">
-        <v>0</v>
+        <v>0.06900000000000001</v>
       </c>
       <c r="W39" t="n">
-        <v>485</v>
+        <v>814</v>
       </c>
       <c r="X39" t="n">
-        <v>11.4</v>
-      </c>
-      <c r="Y39" t="n">
-        <v>5</v>
-      </c>
+        <v>19.5</v>
+      </c>
+      <c r="Y39" t="inlineStr"/>
       <c r="Z39" t="n">
-        <v>22</v>
-      </c>
-      <c r="AA39" t="n">
-        <v>36</v>
-      </c>
+        <v>12.31</v>
+      </c>
+      <c r="AA39" t="inlineStr"/>
       <c r="AB39" t="n">
-        <v>5.75</v>
-      </c>
-      <c r="AC39" t="n">
-        <v>10.7</v>
-      </c>
+        <v>0.8</v>
+      </c>
+      <c r="AC39" t="inlineStr"/>
       <c r="AD39" t="n">
-        <v>0.05</v>
+        <v>0.11</v>
       </c>
       <c r="AE39" t="b">
         <v>1</v>
       </c>
       <c r="AF39" t="n">
-        <v>10</v>
+        <v>12.14</v>
       </c>
       <c r="AG39" t="n">
-        <v>191.6</v>
-      </c>
-      <c r="AH39" t="n">
-        <v>166.91</v>
-      </c>
+        <v>67.17</v>
+      </c>
+      <c r="AH39" t="inlineStr"/>
       <c r="AI39" t="n">
-        <v>41.6</v>
+        <v>30.8</v>
       </c>
       <c r="AJ39" t="n">
-        <v>175.8389566755084</v>
+        <v>64.33497045790251</v>
       </c>
       <c r="AK39" t="n">
-        <v>6.1</v>
+        <v>3</v>
       </c>
       <c r="AL39" t="inlineStr">
         <is>
-          <t>Stale</t>
+          <t>Fresh</t>
         </is>
       </c>
       <c r="AM39" t="inlineStr">
         <is>
-          <t>Stale Accumulation</t>
+          <t>Confirmed Accumulation</t>
         </is>
       </c>
       <c r="AN39" t="inlineStr">
         <is>
-          <t>Late — Poor Entry</t>
+          <t>Confirmed Accumulation</t>
         </is>
       </c>
       <c r="AO39" t="inlineStr">
         <is>
-          <t>25-06-2026</t>
+          <t>17-08-2026</t>
         </is>
       </c>
       <c r="AP39" t="inlineStr">
         <is>
-          <t>25-06-2026</t>
+          <t>18-09-2026</t>
         </is>
       </c>
       <c r="AQ39" t="n">
-        <v>0</v>
+        <v>32</v>
       </c>
       <c r="AR39" t="n">
-        <v>88</v>
+        <v>35</v>
       </c>
       <c r="AS39" t="n">
-        <v>88</v>
+        <v>3</v>
       </c>
       <c r="AT39" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="AU39" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="AV39" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="AW39" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="AX39" t="n">
-        <v>2</v>
+        <v>12</v>
       </c>
       <c r="AY39" t="n">
-        <v>0</v>
+        <v>2601121</v>
       </c>
       <c r="AZ39" t="n">
-        <v>0</v>
+        <v>2601121</v>
       </c>
       <c r="BA39" t="n">
-        <v>0</v>
+        <v>2601121</v>
       </c>
       <c r="BB39" t="n">
-        <v>0</v>
+        <v>8710955</v>
       </c>
       <c r="BC39" t="n">
-        <v>79549544</v>
+        <v>8710955</v>
       </c>
       <c r="BD39" t="n">
         <v>0</v>
@@ -9617,48 +9611,48 @@
         <v>0</v>
       </c>
       <c r="BH39" t="n">
+        <v>0</v>
+      </c>
+      <c r="BI39" t="n">
+        <v>0</v>
+      </c>
+      <c r="BJ39" t="n">
+        <v>0</v>
+      </c>
+      <c r="BK39" t="n">
+        <v>0</v>
+      </c>
+      <c r="BL39" t="n">
+        <v>0</v>
+      </c>
+      <c r="BM39" t="n">
+        <v>0</v>
+      </c>
+      <c r="BN39" t="n">
+        <v>2601121</v>
+      </c>
+      <c r="BO39" t="n">
+        <v>2601121</v>
+      </c>
+      <c r="BP39" t="n">
         <v>4</v>
       </c>
-      <c r="BI39" t="n">
-        <v>0</v>
-      </c>
-      <c r="BJ39" t="n">
-        <v>0</v>
-      </c>
-      <c r="BK39" t="n">
-        <v>0</v>
-      </c>
-      <c r="BL39" t="n">
-        <v>0</v>
-      </c>
-      <c r="BM39" t="n">
-        <v>110497109</v>
-      </c>
-      <c r="BN39" t="n">
-        <v>0</v>
-      </c>
-      <c r="BO39" t="n">
-        <v>0</v>
-      </c>
-      <c r="BP39" t="n">
-        <v>2</v>
-      </c>
       <c r="BQ39" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="BR39" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>HEXAGON</t>
+          <t>VIVIANA</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>HEXAGON NUTRITION LIMITED</t>
+          <t>VIVIANA POWER TECH LIMITED</t>
         </is>
       </c>
       <c r="C40" t="n">
@@ -9670,40 +9664,40 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="F40" t="n">
-        <v>8</v>
+        <v>19</v>
       </c>
       <c r="G40" t="n">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="H40" t="n">
         <v>0</v>
       </c>
       <c r="I40" t="n">
-        <v>66.26000000000001</v>
+        <v>718.8</v>
       </c>
       <c r="J40" t="n">
-        <v>64.48999999999999</v>
+        <v>782.6</v>
       </c>
       <c r="K40" t="n">
-        <v>2.7</v>
+        <v>-8.199999999999999</v>
       </c>
       <c r="L40" t="n">
-        <v>64.29000000000001</v>
+        <v>73.2</v>
       </c>
       <c r="M40" t="n">
-        <v>0.57</v>
+        <v>0.54</v>
       </c>
       <c r="N40" t="n">
-        <v>5656038</v>
+        <v>5375657</v>
       </c>
       <c r="O40" t="n">
         <v>0</v>
       </c>
       <c r="P40" t="n">
-        <v>5656038</v>
+        <v>5375657</v>
       </c>
       <c r="Q40" t="n">
         <v>0</v>
@@ -9717,52 +9711,58 @@
         <v>0</v>
       </c>
       <c r="T40" t="n">
-        <v>9</v>
+        <v>2</v>
       </c>
       <c r="U40" t="inlineStr">
         <is>
-          <t>18-09-2026</t>
+          <t>17-09-2026</t>
         </is>
       </c>
       <c r="V40" t="n">
-        <v>0.06900000000000001</v>
+        <v>0.074</v>
       </c>
       <c r="W40" t="n">
-        <v>814</v>
+        <v>728</v>
       </c>
       <c r="X40" t="n">
-        <v>19.5</v>
-      </c>
-      <c r="Y40" t="inlineStr"/>
+        <v>13.2</v>
+      </c>
+      <c r="Y40" t="n">
+        <v>185</v>
+      </c>
       <c r="Z40" t="n">
-        <v>12.31</v>
-      </c>
-      <c r="AA40" t="inlineStr"/>
+        <v>11.55</v>
+      </c>
+      <c r="AA40" t="n">
+        <v>204</v>
+      </c>
       <c r="AB40" t="n">
-        <v>0.8</v>
-      </c>
-      <c r="AC40" t="inlineStr"/>
+        <v>6.84</v>
+      </c>
+      <c r="AC40" t="n">
+        <v>50.7</v>
+      </c>
       <c r="AD40" t="n">
-        <v>0.11</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="AE40" t="b">
         <v>1</v>
       </c>
       <c r="AF40" t="n">
-        <v>12.14</v>
+        <v>16.07</v>
       </c>
       <c r="AG40" t="n">
-        <v>67.17</v>
+        <v>729.78</v>
       </c>
       <c r="AH40" t="inlineStr"/>
       <c r="AI40" t="n">
-        <v>30.8</v>
+        <v>-20.9</v>
       </c>
       <c r="AJ40" t="n">
-        <v>64.33497045790251</v>
+        <v>782.5967389721939</v>
       </c>
       <c r="AK40" t="n">
-        <v>3</v>
+        <v>-8.199999999999999</v>
       </c>
       <c r="AL40" t="inlineStr">
         <is>
@@ -9781,52 +9781,52 @@
       </c>
       <c r="AO40" t="inlineStr">
         <is>
-          <t>17-08-2026</t>
+          <t>29-06-2026</t>
         </is>
       </c>
       <c r="AP40" t="inlineStr">
         <is>
-          <t>18-09-2026</t>
+          <t>17-09-2026</t>
         </is>
       </c>
       <c r="AQ40" t="n">
-        <v>32</v>
+        <v>80</v>
       </c>
       <c r="AR40" t="n">
-        <v>35</v>
+        <v>84</v>
       </c>
       <c r="AS40" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AT40" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="AU40" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="AV40" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="AW40" t="n">
-        <v>12</v>
+        <v>1</v>
       </c>
       <c r="AX40" t="n">
-        <v>12</v>
+        <v>2</v>
       </c>
       <c r="AY40" t="n">
-        <v>2601121</v>
+        <v>1751854</v>
       </c>
       <c r="AZ40" t="n">
-        <v>2601121</v>
+        <v>1751854</v>
       </c>
       <c r="BA40" t="n">
-        <v>2601121</v>
+        <v>1751854</v>
       </c>
       <c r="BB40" t="n">
-        <v>8710955</v>
+        <v>1751854</v>
       </c>
       <c r="BC40" t="n">
-        <v>8710955</v>
+        <v>5375657</v>
       </c>
       <c r="BD40" t="n">
         <v>0</v>
@@ -9859,13 +9859,13 @@
         <v>0</v>
       </c>
       <c r="BN40" t="n">
-        <v>2601121</v>
+        <v>1751854</v>
       </c>
       <c r="BO40" t="n">
-        <v>2601121</v>
+        <v>1751854</v>
       </c>
       <c r="BP40" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="BQ40" t="n">
         <v>0</v>
@@ -11740,7 +11740,7 @@
         </is>
       </c>
       <c r="C49" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -11748,7 +11748,7 @@
         </is>
       </c>
       <c r="E49" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="F49" t="n">
         <v>8</v>
@@ -11763,25 +11763,25 @@
         <v>81.64</v>
       </c>
       <c r="J49" t="n">
-        <v>92.05</v>
+        <v>91.22</v>
       </c>
       <c r="K49" t="n">
-        <v>-11.3</v>
+        <v>-10.5</v>
       </c>
       <c r="L49" t="n">
         <v>71.72</v>
       </c>
       <c r="M49" t="n">
-        <v>2.3</v>
+        <v>1.37</v>
       </c>
       <c r="N49" t="n">
-        <v>22971294</v>
+        <v>13682958</v>
       </c>
       <c r="O49" t="n">
         <v>0</v>
       </c>
       <c r="P49" t="n">
-        <v>22971294</v>
+        <v>13682958</v>
       </c>
       <c r="Q49" t="n">
         <v>0</v>
@@ -11795,7 +11795,7 @@
         <v>0</v>
       </c>
       <c r="T49" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="U49" t="inlineStr">
         <is>
@@ -11803,7 +11803,7 @@
         </is>
       </c>
       <c r="V49" t="n">
-        <v>0.136</v>
+        <v>0.081</v>
       </c>
       <c r="W49" t="n">
         <v>1692</v>
@@ -11845,10 +11845,10 @@
         <v>-46.7</v>
       </c>
       <c r="AJ49" t="n">
-        <v>91.73975462149539</v>
+        <v>91.21972</v>
       </c>
       <c r="AK49" t="n">
-        <v>-11</v>
+        <v>-10.5</v>
       </c>
       <c r="AL49" t="inlineStr">
         <is>
@@ -11867,7 +11867,7 @@
       </c>
       <c r="AO49" t="inlineStr">
         <is>
-          <t>17-06-2026</t>
+          <t>24-06-2026</t>
         </is>
       </c>
       <c r="AP49" t="inlineStr">
@@ -11876,10 +11876,10 @@
         </is>
       </c>
       <c r="AQ49" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="AR49" t="n">
-        <v>96</v>
+        <v>89</v>
       </c>
       <c r="AS49" t="n">
         <v>89</v>
@@ -13282,35 +13282,35 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>VIVIANA</t>
+          <t>NPST</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>VIVIANA POWER TECH LIMITED</t>
+          <t>NETWORK PEOPLE SERVICES TECHNOLOGIES LIMITED</t>
         </is>
       </c>
       <c r="C31" t="n">
-        <v>718.8</v>
+        <v>1828.5</v>
       </c>
       <c r="D31" t="n">
-        <v>799.47</v>
+        <v>789.9400000000001</v>
       </c>
       <c r="E31" t="n">
-        <v>-10.1</v>
+        <v>131.5</v>
       </c>
       <c r="F31" t="n">
-        <v>73.2</v>
+        <v>67.55</v>
       </c>
       <c r="G31" t="n">
-        <v>1.42</v>
+        <v>12.76</v>
       </c>
       <c r="H31" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>17-09-2026</t>
+          <t>25-06-2026</t>
         </is>
       </c>
     </row>
@@ -13352,35 +13352,35 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>NPST</t>
+          <t>AMANTA</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>NETWORK PEOPLE SERVICES TECHNOLOGIES LIMITED</t>
+          <t>Amanta Healthcare Limited</t>
         </is>
       </c>
       <c r="C33" t="n">
-        <v>1828.5</v>
+        <v>189.95</v>
       </c>
       <c r="D33" t="n">
-        <v>789.9400000000001</v>
+        <v>149.98</v>
       </c>
       <c r="E33" t="n">
-        <v>131.5</v>
+        <v>26.7</v>
       </c>
       <c r="F33" t="n">
-        <v>67.55</v>
+        <v>63.56</v>
       </c>
       <c r="G33" t="n">
-        <v>12.76</v>
+        <v>0.24</v>
       </c>
       <c r="H33" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>25-06-2026</t>
+          <t>18-06-2026</t>
         </is>
       </c>
     </row>
@@ -13457,175 +13457,175 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>AMANTA</t>
+          <t>PLASTIBLEN</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>Amanta Healthcare Limited</t>
+          <t>PLASTIBLENDS INDIA LIMITED</t>
         </is>
       </c>
       <c r="C36" t="n">
-        <v>189.95</v>
+        <v>186.63</v>
       </c>
       <c r="D36" t="n">
-        <v>149.98</v>
+        <v>175.84</v>
       </c>
       <c r="E36" t="n">
-        <v>26.7</v>
+        <v>6.1</v>
       </c>
       <c r="F36" t="n">
-        <v>63.56</v>
+        <v>64.20999999999999</v>
       </c>
       <c r="G36" t="n">
-        <v>0.24</v>
+        <v>7.95</v>
       </c>
       <c r="H36" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>18-06-2026</t>
+          <t>25-06-2026</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>OMPOWER</t>
+          <t>VSTL</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>Om Power Transmission Limited</t>
+          <t>VIBHOR STEEL TUBES LIMITED</t>
         </is>
       </c>
       <c r="C37" t="n">
-        <v>172.37</v>
+        <v>113.54</v>
       </c>
       <c r="D37" t="n">
-        <v>182.69</v>
+        <v>111.01</v>
       </c>
       <c r="E37" t="n">
-        <v>-5.6</v>
+        <v>2.3</v>
       </c>
       <c r="F37" t="n">
-        <v>69.05</v>
+        <v>73.48</v>
       </c>
       <c r="G37" t="n">
-        <v>0.74</v>
+        <v>0.45</v>
       </c>
       <c r="H37" t="n">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>24-06-2026</t>
+          <t>03-09-2026</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>VSTL</t>
+          <t>OMPOWER</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>VIBHOR STEEL TUBES LIMITED</t>
+          <t>Om Power Transmission Limited</t>
         </is>
       </c>
       <c r="C38" t="n">
-        <v>113.54</v>
+        <v>172.37</v>
       </c>
       <c r="D38" t="n">
-        <v>111.01</v>
+        <v>182.69</v>
       </c>
       <c r="E38" t="n">
-        <v>2.3</v>
+        <v>-5.6</v>
       </c>
       <c r="F38" t="n">
-        <v>73.48</v>
+        <v>69.05</v>
       </c>
       <c r="G38" t="n">
-        <v>0.45</v>
+        <v>0.74</v>
       </c>
       <c r="H38" t="n">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="I38" t="inlineStr">
         <is>
-          <t>03-09-2026</t>
+          <t>24-06-2026</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>PLASTIBLEN</t>
+          <t>HEXAGON</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>PLASTIBLENDS INDIA LIMITED</t>
+          <t>HEXAGON NUTRITION LIMITED</t>
         </is>
       </c>
       <c r="C39" t="n">
-        <v>186.63</v>
+        <v>66.26000000000001</v>
       </c>
       <c r="D39" t="n">
-        <v>175.84</v>
+        <v>64.48999999999999</v>
       </c>
       <c r="E39" t="n">
-        <v>6.1</v>
+        <v>2.7</v>
       </c>
       <c r="F39" t="n">
-        <v>64.20999999999999</v>
+        <v>64.29000000000001</v>
       </c>
       <c r="G39" t="n">
-        <v>7.95</v>
+        <v>0.57</v>
       </c>
       <c r="H39" t="n">
-        <v>2</v>
+        <v>9</v>
       </c>
       <c r="I39" t="inlineStr">
         <is>
-          <t>25-06-2026</t>
+          <t>18-09-2026</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>HEXAGON</t>
+          <t>VIVIANA</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>HEXAGON NUTRITION LIMITED</t>
+          <t>VIVIANA POWER TECH LIMITED</t>
         </is>
       </c>
       <c r="C40" t="n">
-        <v>66.26000000000001</v>
+        <v>718.8</v>
       </c>
       <c r="D40" t="n">
-        <v>64.48999999999999</v>
+        <v>782.6</v>
       </c>
       <c r="E40" t="n">
-        <v>2.7</v>
+        <v>-8.199999999999999</v>
       </c>
       <c r="F40" t="n">
-        <v>64.29000000000001</v>
+        <v>73.2</v>
       </c>
       <c r="G40" t="n">
-        <v>0.57</v>
+        <v>0.54</v>
       </c>
       <c r="H40" t="n">
-        <v>9</v>
+        <v>2</v>
       </c>
       <c r="I40" t="inlineStr">
         <is>
-          <t>18-09-2026</t>
+          <t>17-09-2026</t>
         </is>
       </c>
     </row>
@@ -13924,19 +13924,19 @@
         <v>81.64</v>
       </c>
       <c r="D49" t="n">
-        <v>92.05</v>
+        <v>91.22</v>
       </c>
       <c r="E49" t="n">
-        <v>-11.3</v>
+        <v>-10.5</v>
       </c>
       <c r="F49" t="n">
         <v>71.72</v>
       </c>
       <c r="G49" t="n">
-        <v>2.3</v>
+        <v>1.37</v>
       </c>
       <c r="H49" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I49" t="inlineStr">
         <is>
@@ -14012,7 +14012,7 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>29</v>
+        <v>30</v>
       </c>
     </row>
     <row r="3">
@@ -14022,7 +14022,7 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
     </row>
     <row r="4">

--- a/output/2026-09-21/enriched_analysis.xlsx
+++ b/output/2026-09-21/enriched_analysis.xlsx
@@ -929,13 +929,13 @@
         </is>
       </c>
       <c r="V2" t="n">
-        <v>3.467</v>
+        <v>3.526</v>
       </c>
       <c r="W2" t="n">
-        <v>3055</v>
+        <v>3004</v>
       </c>
       <c r="X2" t="n">
-        <v>23.9</v>
+        <v>23.5</v>
       </c>
       <c r="Y2" t="n">
         <v>75</v>
@@ -1161,13 +1161,13 @@
         </is>
       </c>
       <c r="V3" t="n">
-        <v>0.049</v>
+        <v>0.05</v>
       </c>
       <c r="W3" t="n">
-        <v>2703</v>
+        <v>2662</v>
       </c>
       <c r="X3" t="n">
-        <v>9.289999999999999</v>
+        <v>9.17</v>
       </c>
       <c r="Y3" t="n">
         <v>36</v>
@@ -1393,13 +1393,13 @@
         </is>
       </c>
       <c r="V4" t="n">
-        <v>0.368</v>
+        <v>0.362</v>
       </c>
       <c r="W4" t="n">
-        <v>2635</v>
+        <v>2685</v>
       </c>
       <c r="X4" t="n">
-        <v>21.6</v>
+        <v>22</v>
       </c>
       <c r="Y4" t="n">
         <v>8</v>
@@ -1625,13 +1625,13 @@
         </is>
       </c>
       <c r="V5" t="n">
-        <v>0.9</v>
+        <v>0.875</v>
       </c>
       <c r="W5" t="n">
-        <v>206</v>
+        <v>212</v>
       </c>
       <c r="X5" t="n">
-        <v>8.76</v>
+        <v>9.01</v>
       </c>
       <c r="Y5" t="n">
         <v>17</v>
@@ -1857,13 +1857,13 @@
         </is>
       </c>
       <c r="V6" t="n">
-        <v>0.132</v>
+        <v>0.121</v>
       </c>
       <c r="W6" t="n">
-        <v>2377</v>
+        <v>2597</v>
       </c>
       <c r="X6" t="n">
-        <v>20.8</v>
+        <v>22.8</v>
       </c>
       <c r="Y6" t="n">
         <v>-3</v>
@@ -2089,13 +2089,13 @@
         </is>
       </c>
       <c r="V7" t="n">
-        <v>0.056</v>
+        <v>0.053</v>
       </c>
       <c r="W7" t="n">
-        <v>1461</v>
+        <v>1545</v>
       </c>
       <c r="X7" t="n">
-        <v>19.7</v>
+        <v>20.8</v>
       </c>
       <c r="Y7" t="n">
         <v>55</v>
@@ -2481,12 +2481,12 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>SRHHYPOLTD</t>
+          <t>PKTEA</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Sree Rayalaseema Hi-Strength Hypo Limited</t>
+          <t>THE PERIA KARAMALAI TEA &amp; PRODUCE COMPANY LIMITED</t>
         </is>
       </c>
       <c r="C9" t="n">
@@ -2510,28 +2510,28 @@
         <v>0</v>
       </c>
       <c r="I9" t="n">
-        <v>523.1</v>
+        <v>910</v>
       </c>
       <c r="J9" t="n">
-        <v>509.48</v>
+        <v>734.17</v>
       </c>
       <c r="K9" t="n">
-        <v>2.7</v>
+        <v>23.9</v>
       </c>
       <c r="L9" t="n">
-        <v>62.09</v>
+        <v>61.71</v>
       </c>
       <c r="M9" t="n">
-        <v>2.8</v>
+        <v>2.13</v>
       </c>
       <c r="N9" t="n">
-        <v>27987060</v>
+        <v>21291589</v>
       </c>
       <c r="O9" t="n">
         <v>0</v>
       </c>
       <c r="P9" t="n">
-        <v>27987060</v>
+        <v>21291589</v>
       </c>
       <c r="Q9" t="n">
         <v>0</v>
@@ -2545,64 +2545,62 @@
         <v>0</v>
       </c>
       <c r="T9" t="n">
-        <v>16</v>
+        <v>4</v>
       </c>
       <c r="U9" t="inlineStr">
         <is>
-          <t>18-09-2026</t>
+          <t>04-09-2026</t>
         </is>
       </c>
       <c r="V9" t="n">
-        <v>0.312</v>
+        <v>0.719</v>
       </c>
       <c r="W9" t="n">
-        <v>898</v>
-      </c>
-      <c r="X9" t="n">
-        <v>8.83</v>
-      </c>
+        <v>296</v>
+      </c>
+      <c r="X9" t="inlineStr"/>
       <c r="Y9" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="Z9" t="n">
-        <v>30</v>
+        <v>11.91</v>
       </c>
       <c r="AA9" t="n">
-        <v>0</v>
+        <v>-184</v>
       </c>
       <c r="AB9" t="n">
-        <v>14.66</v>
+        <v>31.98</v>
       </c>
       <c r="AC9" t="n">
-        <v>14.4</v>
+        <v>-0.26</v>
       </c>
       <c r="AD9" t="n">
-        <v>0.01</v>
+        <v>0.1</v>
       </c>
       <c r="AE9" t="b">
         <v>1</v>
       </c>
       <c r="AF9" t="n">
-        <v>14</v>
+        <v>57.93</v>
       </c>
       <c r="AG9" t="n">
-        <v>495.46</v>
+        <v>773.98</v>
       </c>
       <c r="AH9" t="n">
-        <v>487.98</v>
+        <v>776.91</v>
       </c>
       <c r="AI9" t="n">
-        <v>20.7</v>
+        <v>17.6</v>
       </c>
       <c r="AJ9" t="n">
-        <v>509.476271093878</v>
+        <v>725.7771441605839</v>
       </c>
       <c r="AK9" t="n">
-        <v>2.7</v>
+        <v>25.4</v>
       </c>
       <c r="AL9" t="inlineStr">
         <is>
-          <t>Fresh</t>
+          <t>Active</t>
         </is>
       </c>
       <c r="AM9" t="inlineStr">
@@ -2612,57 +2610,57 @@
       </c>
       <c r="AN9" t="inlineStr">
         <is>
-          <t>Confirmed Accumulation</t>
+          <t>Late — Poor Entry</t>
         </is>
       </c>
       <c r="AO9" t="inlineStr">
         <is>
-          <t>26-08-2026</t>
+          <t>17-08-2026</t>
         </is>
       </c>
       <c r="AP9" t="inlineStr">
         <is>
-          <t>18-09-2026</t>
+          <t>04-09-2026</t>
         </is>
       </c>
       <c r="AQ9" t="n">
-        <v>23</v>
+        <v>18</v>
       </c>
       <c r="AR9" t="n">
-        <v>26</v>
+        <v>35</v>
       </c>
       <c r="AS9" t="n">
-        <v>3</v>
+        <v>17</v>
       </c>
       <c r="AT9" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="AU9" t="n">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="AV9" t="n">
-        <v>16</v>
+        <v>1</v>
       </c>
       <c r="AW9" t="n">
-        <v>16</v>
+        <v>5</v>
       </c>
       <c r="AX9" t="n">
-        <v>16</v>
+        <v>5</v>
       </c>
       <c r="AY9" t="n">
-        <v>10676672</v>
+        <v>0</v>
       </c>
       <c r="AZ9" t="n">
-        <v>20024685</v>
+        <v>0</v>
       </c>
       <c r="BA9" t="n">
-        <v>27987060</v>
+        <v>5174686</v>
       </c>
       <c r="BB9" t="n">
-        <v>27987060</v>
+        <v>28636263</v>
       </c>
       <c r="BC9" t="n">
-        <v>27987060</v>
+        <v>28636263</v>
       </c>
       <c r="BD9" t="n">
         <v>0</v>
@@ -2695,34 +2693,34 @@
         <v>0</v>
       </c>
       <c r="BN9" t="n">
-        <v>10676672</v>
+        <v>0</v>
       </c>
       <c r="BO9" t="n">
-        <v>27987060</v>
+        <v>5174686</v>
       </c>
       <c r="BP9" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="BQ9" t="n">
         <v>0</v>
       </c>
       <c r="BR9" t="n">
-        <v>0.3815</v>
+        <v>0</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>PKTEA</t>
+          <t>THANGAMAYL</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>THE PERIA KARAMALAI TEA &amp; PRODUCE COMPANY LIMITED</t>
+          <t>THANGAMAYIL JEWELLERY LIMITED</t>
         </is>
       </c>
       <c r="C10" t="n">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -2730,140 +2728,142 @@
         </is>
       </c>
       <c r="E10" t="n">
+        <v>5</v>
+      </c>
+      <c r="F10" t="n">
+        <v>27</v>
+      </c>
+      <c r="G10" t="n">
         <v>13</v>
       </c>
-      <c r="F10" t="n">
-        <v>12</v>
-      </c>
-      <c r="G10" t="n">
+      <c r="H10" t="n">
+        <v>0</v>
+      </c>
+      <c r="I10" t="n">
+        <v>5044.5</v>
+      </c>
+      <c r="J10" t="n">
+        <v>5198.76</v>
+      </c>
+      <c r="K10" t="n">
+        <v>-3</v>
+      </c>
+      <c r="L10" t="n">
+        <v>67.16</v>
+      </c>
+      <c r="M10" t="n">
+        <v>7.21</v>
+      </c>
+      <c r="N10" t="n">
+        <v>72054758</v>
+      </c>
+      <c r="O10" t="n">
+        <v>0</v>
+      </c>
+      <c r="P10" t="n">
+        <v>72054758</v>
+      </c>
+      <c r="Q10" t="n">
+        <v>0</v>
+      </c>
+      <c r="R10" t="inlineStr">
+        <is>
+          <t>Net Buying</t>
+        </is>
+      </c>
+      <c r="S10" t="b">
+        <v>0</v>
+      </c>
+      <c r="T10" t="n">
+        <v>6</v>
+      </c>
+      <c r="U10" t="inlineStr">
+        <is>
+          <t>31-08-2026</t>
+        </is>
+      </c>
+      <c r="V10" t="n">
+        <v>0.047</v>
+      </c>
+      <c r="W10" t="n">
+        <v>15306</v>
+      </c>
+      <c r="X10" t="n">
+        <v>39</v>
+      </c>
+      <c r="Y10" t="n">
+        <v>83</v>
+      </c>
+      <c r="Z10" t="n">
+        <v>145</v>
+      </c>
+      <c r="AA10" t="n">
+        <v>264</v>
+      </c>
+      <c r="AB10" t="n">
+        <v>27.38</v>
+      </c>
+      <c r="AC10" t="n">
+        <v>25.5</v>
+      </c>
+      <c r="AD10" t="n">
+        <v>0.64</v>
+      </c>
+      <c r="AE10" t="b">
+        <v>1</v>
+      </c>
+      <c r="AF10" t="n">
+        <v>5</v>
+      </c>
+      <c r="AG10" t="n">
+        <v>5648.59</v>
+      </c>
+      <c r="AH10" t="n">
+        <v>4410.23</v>
+      </c>
+      <c r="AI10" t="n">
+        <v>46.3</v>
+      </c>
+      <c r="AJ10" t="n">
+        <v>5198.755988455989</v>
+      </c>
+      <c r="AK10" t="n">
+        <v>-3</v>
+      </c>
+      <c r="AL10" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="AM10" t="inlineStr">
+        <is>
+          <t>Confirmed Accumulation</t>
+        </is>
+      </c>
+      <c r="AN10" t="inlineStr">
+        <is>
+          <t>Confirmed Accumulation</t>
+        </is>
+      </c>
+      <c r="AO10" t="inlineStr">
+        <is>
+          <t>04-08-2026</t>
+        </is>
+      </c>
+      <c r="AP10" t="inlineStr">
+        <is>
+          <t>31-08-2026</t>
+        </is>
+      </c>
+      <c r="AQ10" t="n">
+        <v>27</v>
+      </c>
+      <c r="AR10" t="n">
+        <v>48</v>
+      </c>
+      <c r="AS10" t="n">
         <v>21</v>
       </c>
-      <c r="H10" t="n">
-        <v>0</v>
-      </c>
-      <c r="I10" t="n">
-        <v>910</v>
-      </c>
-      <c r="J10" t="n">
-        <v>734.17</v>
-      </c>
-      <c r="K10" t="n">
-        <v>23.9</v>
-      </c>
-      <c r="L10" t="n">
-        <v>61.71</v>
-      </c>
-      <c r="M10" t="n">
-        <v>2.13</v>
-      </c>
-      <c r="N10" t="n">
-        <v>21291589</v>
-      </c>
-      <c r="O10" t="n">
-        <v>0</v>
-      </c>
-      <c r="P10" t="n">
-        <v>21291589</v>
-      </c>
-      <c r="Q10" t="n">
-        <v>0</v>
-      </c>
-      <c r="R10" t="inlineStr">
-        <is>
-          <t>Net Buying</t>
-        </is>
-      </c>
-      <c r="S10" t="b">
-        <v>0</v>
-      </c>
-      <c r="T10" t="n">
-        <v>4</v>
-      </c>
-      <c r="U10" t="inlineStr">
-        <is>
-          <t>04-09-2026</t>
-        </is>
-      </c>
-      <c r="V10" t="n">
-        <v>0.755</v>
-      </c>
-      <c r="W10" t="n">
-        <v>282</v>
-      </c>
-      <c r="X10" t="inlineStr"/>
-      <c r="Y10" t="n">
-        <v>9</v>
-      </c>
-      <c r="Z10" t="n">
-        <v>11.91</v>
-      </c>
-      <c r="AA10" t="n">
-        <v>-184</v>
-      </c>
-      <c r="AB10" t="n">
-        <v>31.98</v>
-      </c>
-      <c r="AC10" t="n">
-        <v>-0.26</v>
-      </c>
-      <c r="AD10" t="n">
-        <v>0.1</v>
-      </c>
-      <c r="AE10" t="b">
-        <v>1</v>
-      </c>
-      <c r="AF10" t="n">
-        <v>57.93</v>
-      </c>
-      <c r="AG10" t="n">
-        <v>773.98</v>
-      </c>
-      <c r="AH10" t="n">
-        <v>776.91</v>
-      </c>
-      <c r="AI10" t="n">
-        <v>17.6</v>
-      </c>
-      <c r="AJ10" t="n">
-        <v>725.7771441605839</v>
-      </c>
-      <c r="AK10" t="n">
-        <v>25.4</v>
-      </c>
-      <c r="AL10" t="inlineStr">
-        <is>
-          <t>Active</t>
-        </is>
-      </c>
-      <c r="AM10" t="inlineStr">
-        <is>
-          <t>Confirmed Accumulation</t>
-        </is>
-      </c>
-      <c r="AN10" t="inlineStr">
-        <is>
-          <t>Late — Poor Entry</t>
-        </is>
-      </c>
-      <c r="AO10" t="inlineStr">
-        <is>
-          <t>17-08-2026</t>
-        </is>
-      </c>
-      <c r="AP10" t="inlineStr">
-        <is>
-          <t>04-09-2026</t>
-        </is>
-      </c>
-      <c r="AQ10" t="n">
-        <v>18</v>
-      </c>
-      <c r="AR10" t="n">
-        <v>35</v>
-      </c>
-      <c r="AS10" t="n">
-        <v>17</v>
-      </c>
       <c r="AT10" t="n">
         <v>0</v>
       </c>
@@ -2871,13 +2871,13 @@
         <v>0</v>
       </c>
       <c r="AV10" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AW10" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AX10" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AY10" t="n">
         <v>0</v>
@@ -2886,13 +2886,13 @@
         <v>0</v>
       </c>
       <c r="BA10" t="n">
-        <v>5174686</v>
+        <v>19879002</v>
       </c>
       <c r="BB10" t="n">
-        <v>28636263</v>
+        <v>72054758</v>
       </c>
       <c r="BC10" t="n">
-        <v>28636263</v>
+        <v>72054758</v>
       </c>
       <c r="BD10" t="n">
         <v>0</v>
@@ -2928,10 +2928,10 @@
         <v>0</v>
       </c>
       <c r="BO10" t="n">
-        <v>5174686</v>
+        <v>19879002</v>
       </c>
       <c r="BP10" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="BQ10" t="n">
         <v>0</v>
@@ -2943,12 +2943,12 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>STEL</t>
+          <t>OBCL</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>STEL HOLDINGS LIMITED</t>
+          <t>OBCL LIMITED</t>
         </is>
       </c>
       <c r="C11" t="n">
@@ -2960,40 +2960,40 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>13</v>
+        <v>20</v>
       </c>
       <c r="F11" t="n">
-        <v>13</v>
+        <v>5</v>
       </c>
       <c r="G11" t="n">
         <v>21</v>
       </c>
       <c r="H11" t="n">
-        <v>-2</v>
+        <v>-1</v>
       </c>
       <c r="I11" t="n">
-        <v>654.2</v>
+        <v>57.02</v>
       </c>
       <c r="J11" t="n">
-        <v>625.41</v>
+        <v>53.45</v>
       </c>
       <c r="K11" t="n">
-        <v>4.6</v>
+        <v>6.7</v>
       </c>
       <c r="L11" t="n">
-        <v>64.68000000000001</v>
+        <v>67.23</v>
       </c>
       <c r="M11" t="n">
-        <v>3.96</v>
+        <v>1.95</v>
       </c>
       <c r="N11" t="n">
-        <v>39558097</v>
+        <v>19457263</v>
       </c>
       <c r="O11" t="n">
         <v>0</v>
       </c>
       <c r="P11" t="n">
-        <v>39558097</v>
+        <v>19457263</v>
       </c>
       <c r="Q11" t="n">
         <v>0</v>
@@ -3007,60 +3007,58 @@
         <v>0</v>
       </c>
       <c r="T11" t="n">
-        <v>33</v>
+        <v>11</v>
       </c>
       <c r="U11" t="inlineStr">
         <is>
-          <t>18-09-2026</t>
+          <t>15-09-2026</t>
         </is>
       </c>
       <c r="V11" t="n">
-        <v>0.328</v>
+        <v>1.595</v>
       </c>
       <c r="W11" t="n">
-        <v>1207</v>
-      </c>
-      <c r="X11" t="n">
-        <v>61.5</v>
-      </c>
+        <v>122</v>
+      </c>
+      <c r="X11" t="inlineStr"/>
       <c r="Y11" t="n">
-        <v>21</v>
+        <v>6</v>
       </c>
       <c r="Z11" t="n">
-        <v>-0.11</v>
+        <v>2.47</v>
       </c>
       <c r="AA11" t="n">
-        <v>23</v>
+        <v>-3779</v>
       </c>
       <c r="AB11" t="n">
-        <v>-0.07000000000000001</v>
+        <v>-0.05</v>
       </c>
       <c r="AC11" t="n">
-        <v>1.58</v>
+        <v>-1.26</v>
       </c>
       <c r="AD11" t="n">
-        <v>0</v>
+        <v>0.8</v>
       </c>
       <c r="AE11" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AF11" t="n">
-        <v>-110</v>
+        <v>3</v>
       </c>
       <c r="AG11" t="n">
-        <v>581.76</v>
+        <v>54.24</v>
       </c>
       <c r="AH11" t="n">
-        <v>515.16</v>
+        <v>55.16</v>
       </c>
       <c r="AI11" t="n">
-        <v>46.1</v>
+        <v>2.6</v>
       </c>
       <c r="AJ11" t="n">
-        <v>625.4145705206241</v>
+        <v>53.44741172107844</v>
       </c>
       <c r="AK11" t="n">
-        <v>4.6</v>
+        <v>6.7</v>
       </c>
       <c r="AL11" t="inlineStr">
         <is>
@@ -3079,52 +3077,52 @@
       </c>
       <c r="AO11" t="inlineStr">
         <is>
-          <t>19-06-2026</t>
+          <t>05-08-2026</t>
         </is>
       </c>
       <c r="AP11" t="inlineStr">
         <is>
-          <t>18-09-2026</t>
+          <t>15-09-2026</t>
         </is>
       </c>
       <c r="AQ11" t="n">
-        <v>91</v>
+        <v>41</v>
       </c>
       <c r="AR11" t="n">
-        <v>94</v>
+        <v>47</v>
       </c>
       <c r="AS11" t="n">
+        <v>6</v>
+      </c>
+      <c r="AT11" t="n">
+        <v>1</v>
+      </c>
+      <c r="AU11" t="n">
         <v>3</v>
       </c>
-      <c r="AT11" t="n">
-        <v>4</v>
-      </c>
-      <c r="AU11" t="n">
-        <v>7</v>
-      </c>
       <c r="AV11" t="n">
-        <v>19</v>
+        <v>5</v>
       </c>
       <c r="AW11" t="n">
-        <v>29</v>
+        <v>11</v>
       </c>
       <c r="AX11" t="n">
-        <v>31</v>
+        <v>11</v>
       </c>
       <c r="AY11" t="n">
-        <v>6908288</v>
+        <v>789002</v>
       </c>
       <c r="AZ11" t="n">
-        <v>9395107</v>
+        <v>1412746</v>
       </c>
       <c r="BA11" t="n">
-        <v>22368301</v>
+        <v>2942912</v>
       </c>
       <c r="BB11" t="n">
-        <v>28676708</v>
+        <v>19457263</v>
       </c>
       <c r="BC11" t="n">
-        <v>35288088</v>
+        <v>19457263</v>
       </c>
       <c r="BD11" t="n">
         <v>0</v>
@@ -3157,30 +3155,30 @@
         <v>0</v>
       </c>
       <c r="BN11" t="n">
-        <v>6908288</v>
+        <v>789002</v>
       </c>
       <c r="BO11" t="n">
-        <v>22368301</v>
+        <v>2942912</v>
       </c>
       <c r="BP11" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="BQ11" t="n">
         <v>0</v>
       </c>
       <c r="BR11" t="n">
-        <v>0.3088</v>
+        <v>0.2681</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>THANGAMAYL</t>
+          <t>STEL</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>THANGAMAYIL JEWELLERY LIMITED</t>
+          <t>STEL HOLDINGS LIMITED</t>
         </is>
       </c>
       <c r="C12" t="n">
@@ -3192,40 +3190,40 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>5</v>
+        <v>13</v>
       </c>
       <c r="F12" t="n">
-        <v>27</v>
+        <v>13</v>
       </c>
       <c r="G12" t="n">
-        <v>13</v>
+        <v>21</v>
       </c>
       <c r="H12" t="n">
-        <v>0</v>
+        <v>-2</v>
       </c>
       <c r="I12" t="n">
-        <v>5044.5</v>
+        <v>654.2</v>
       </c>
       <c r="J12" t="n">
-        <v>5198.76</v>
+        <v>625.41</v>
       </c>
       <c r="K12" t="n">
-        <v>-3</v>
+        <v>4.6</v>
       </c>
       <c r="L12" t="n">
-        <v>67.16</v>
+        <v>64.68000000000001</v>
       </c>
       <c r="M12" t="n">
-        <v>7.21</v>
+        <v>3.96</v>
       </c>
       <c r="N12" t="n">
-        <v>72054758</v>
+        <v>39558097</v>
       </c>
       <c r="O12" t="n">
         <v>0</v>
       </c>
       <c r="P12" t="n">
-        <v>72054758</v>
+        <v>39558097</v>
       </c>
       <c r="Q12" t="n">
         <v>0</v>
@@ -3239,64 +3237,64 @@
         <v>0</v>
       </c>
       <c r="T12" t="n">
-        <v>6</v>
+        <v>33</v>
       </c>
       <c r="U12" t="inlineStr">
         <is>
-          <t>31-08-2026</t>
+          <t>18-09-2026</t>
         </is>
       </c>
       <c r="V12" t="n">
-        <v>0.046</v>
+        <v>0.325</v>
       </c>
       <c r="W12" t="n">
-        <v>15679</v>
+        <v>1219</v>
       </c>
       <c r="X12" t="n">
-        <v>39.9</v>
+        <v>62.1</v>
       </c>
       <c r="Y12" t="n">
-        <v>83</v>
+        <v>21</v>
       </c>
       <c r="Z12" t="n">
-        <v>145</v>
+        <v>-0.11</v>
       </c>
       <c r="AA12" t="n">
-        <v>264</v>
+        <v>23</v>
       </c>
       <c r="AB12" t="n">
-        <v>27.38</v>
+        <v>-0.07000000000000001</v>
       </c>
       <c r="AC12" t="n">
-        <v>25.5</v>
+        <v>1.58</v>
       </c>
       <c r="AD12" t="n">
-        <v>0.64</v>
+        <v>0</v>
       </c>
       <c r="AE12" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AF12" t="n">
-        <v>5</v>
+        <v>-110</v>
       </c>
       <c r="AG12" t="n">
-        <v>5648.59</v>
+        <v>581.76</v>
       </c>
       <c r="AH12" t="n">
-        <v>4410.23</v>
+        <v>515.16</v>
       </c>
       <c r="AI12" t="n">
-        <v>46.3</v>
+        <v>46.1</v>
       </c>
       <c r="AJ12" t="n">
-        <v>5198.755988455989</v>
+        <v>625.4145705206241</v>
       </c>
       <c r="AK12" t="n">
-        <v>-3</v>
+        <v>4.6</v>
       </c>
       <c r="AL12" t="inlineStr">
         <is>
-          <t>Active</t>
+          <t>Fresh</t>
         </is>
       </c>
       <c r="AM12" t="inlineStr">
@@ -3311,112 +3309,112 @@
       </c>
       <c r="AO12" t="inlineStr">
         <is>
-          <t>04-08-2026</t>
+          <t>19-06-2026</t>
         </is>
       </c>
       <c r="AP12" t="inlineStr">
         <is>
-          <t>31-08-2026</t>
+          <t>18-09-2026</t>
         </is>
       </c>
       <c r="AQ12" t="n">
-        <v>27</v>
+        <v>91</v>
       </c>
       <c r="AR12" t="n">
-        <v>48</v>
+        <v>94</v>
       </c>
       <c r="AS12" t="n">
-        <v>21</v>
+        <v>3</v>
       </c>
       <c r="AT12" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="AU12" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="AV12" t="n">
+        <v>19</v>
+      </c>
+      <c r="AW12" t="n">
+        <v>29</v>
+      </c>
+      <c r="AX12" t="n">
+        <v>31</v>
+      </c>
+      <c r="AY12" t="n">
+        <v>6908288</v>
+      </c>
+      <c r="AZ12" t="n">
+        <v>9395107</v>
+      </c>
+      <c r="BA12" t="n">
+        <v>22368301</v>
+      </c>
+      <c r="BB12" t="n">
+        <v>28676708</v>
+      </c>
+      <c r="BC12" t="n">
+        <v>35288088</v>
+      </c>
+      <c r="BD12" t="n">
+        <v>0</v>
+      </c>
+      <c r="BE12" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF12" t="n">
+        <v>0</v>
+      </c>
+      <c r="BG12" t="n">
+        <v>0</v>
+      </c>
+      <c r="BH12" t="n">
+        <v>0</v>
+      </c>
+      <c r="BI12" t="n">
+        <v>0</v>
+      </c>
+      <c r="BJ12" t="n">
+        <v>0</v>
+      </c>
+      <c r="BK12" t="n">
+        <v>0</v>
+      </c>
+      <c r="BL12" t="n">
+        <v>0</v>
+      </c>
+      <c r="BM12" t="n">
+        <v>0</v>
+      </c>
+      <c r="BN12" t="n">
+        <v>6908288</v>
+      </c>
+      <c r="BO12" t="n">
+        <v>22368301</v>
+      </c>
+      <c r="BP12" t="n">
         <v>2</v>
       </c>
-      <c r="AW12" t="n">
-        <v>6</v>
-      </c>
-      <c r="AX12" t="n">
-        <v>6</v>
-      </c>
-      <c r="AY12" t="n">
-        <v>0</v>
-      </c>
-      <c r="AZ12" t="n">
-        <v>0</v>
-      </c>
-      <c r="BA12" t="n">
-        <v>19879002</v>
-      </c>
-      <c r="BB12" t="n">
-        <v>72054758</v>
-      </c>
-      <c r="BC12" t="n">
-        <v>72054758</v>
-      </c>
-      <c r="BD12" t="n">
-        <v>0</v>
-      </c>
-      <c r="BE12" t="n">
-        <v>0</v>
-      </c>
-      <c r="BF12" t="n">
-        <v>0</v>
-      </c>
-      <c r="BG12" t="n">
-        <v>0</v>
-      </c>
-      <c r="BH12" t="n">
-        <v>0</v>
-      </c>
-      <c r="BI12" t="n">
-        <v>0</v>
-      </c>
-      <c r="BJ12" t="n">
-        <v>0</v>
-      </c>
-      <c r="BK12" t="n">
-        <v>0</v>
-      </c>
-      <c r="BL12" t="n">
-        <v>0</v>
-      </c>
-      <c r="BM12" t="n">
-        <v>0</v>
-      </c>
-      <c r="BN12" t="n">
-        <v>0</v>
-      </c>
-      <c r="BO12" t="n">
-        <v>19879002</v>
-      </c>
-      <c r="BP12" t="n">
-        <v>3</v>
-      </c>
       <c r="BQ12" t="n">
         <v>0</v>
       </c>
       <c r="BR12" t="n">
-        <v>0</v>
+        <v>0.3088</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>OBCL</t>
+          <t>SRHHYPOLTD</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>OBCL LIMITED</t>
+          <t>Sree Rayalaseema Hi-Strength Hypo Limited</t>
         </is>
       </c>
       <c r="C13" t="n">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -3424,40 +3422,40 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>20</v>
+        <v>11</v>
       </c>
       <c r="F13" t="n">
-        <v>5</v>
+        <v>12</v>
       </c>
       <c r="G13" t="n">
         <v>21</v>
       </c>
       <c r="H13" t="n">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="I13" t="n">
-        <v>57.02</v>
+        <v>523.1</v>
       </c>
       <c r="J13" t="n">
-        <v>53.45</v>
+        <v>509.48</v>
       </c>
       <c r="K13" t="n">
-        <v>6.7</v>
+        <v>2.7</v>
       </c>
       <c r="L13" t="n">
-        <v>67.23</v>
+        <v>62.09</v>
       </c>
       <c r="M13" t="n">
-        <v>1.95</v>
+        <v>2.8</v>
       </c>
       <c r="N13" t="n">
-        <v>19457263</v>
+        <v>27987060</v>
       </c>
       <c r="O13" t="n">
         <v>0</v>
       </c>
       <c r="P13" t="n">
-        <v>19457263</v>
+        <v>27987060</v>
       </c>
       <c r="Q13" t="n">
         <v>0</v>
@@ -3471,122 +3469,124 @@
         <v>0</v>
       </c>
       <c r="T13" t="n">
-        <v>11</v>
+        <v>16</v>
       </c>
       <c r="U13" t="inlineStr">
         <is>
-          <t>15-09-2026</t>
+          <t>18-09-2026</t>
         </is>
       </c>
       <c r="V13" t="n">
-        <v>1.621</v>
+        <v>0.292</v>
       </c>
       <c r="W13" t="n">
-        <v>120</v>
-      </c>
-      <c r="X13" t="inlineStr"/>
+        <v>958</v>
+      </c>
+      <c r="X13" t="n">
+        <v>9.44</v>
+      </c>
       <c r="Y13" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="Z13" t="n">
-        <v>2.47</v>
+        <v>30</v>
       </c>
       <c r="AA13" t="n">
-        <v>-3779</v>
+        <v>0</v>
       </c>
       <c r="AB13" t="n">
-        <v>-0.05</v>
+        <v>14.66</v>
       </c>
       <c r="AC13" t="n">
-        <v>-1.26</v>
+        <v>14.4</v>
       </c>
       <c r="AD13" t="n">
-        <v>0.8</v>
+        <v>0.01</v>
       </c>
       <c r="AE13" t="b">
         <v>1</v>
       </c>
       <c r="AF13" t="n">
+        <v>14</v>
+      </c>
+      <c r="AG13" t="n">
+        <v>495.46</v>
+      </c>
+      <c r="AH13" t="n">
+        <v>487.98</v>
+      </c>
+      <c r="AI13" t="n">
+        <v>20.7</v>
+      </c>
+      <c r="AJ13" t="n">
+        <v>509.476271093878</v>
+      </c>
+      <c r="AK13" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="AL13" t="inlineStr">
+        <is>
+          <t>Fresh</t>
+        </is>
+      </c>
+      <c r="AM13" t="inlineStr">
+        <is>
+          <t>Confirmed Accumulation</t>
+        </is>
+      </c>
+      <c r="AN13" t="inlineStr">
+        <is>
+          <t>Confirmed Accumulation</t>
+        </is>
+      </c>
+      <c r="AO13" t="inlineStr">
+        <is>
+          <t>26-08-2026</t>
+        </is>
+      </c>
+      <c r="AP13" t="inlineStr">
+        <is>
+          <t>18-09-2026</t>
+        </is>
+      </c>
+      <c r="AQ13" t="n">
+        <v>23</v>
+      </c>
+      <c r="AR13" t="n">
+        <v>26</v>
+      </c>
+      <c r="AS13" t="n">
         <v>3</v>
       </c>
-      <c r="AG13" t="n">
-        <v>54.24</v>
-      </c>
-      <c r="AH13" t="n">
-        <v>55.16</v>
-      </c>
-      <c r="AI13" t="n">
-        <v>2.6</v>
-      </c>
-      <c r="AJ13" t="n">
-        <v>53.44741172107844</v>
-      </c>
-      <c r="AK13" t="n">
-        <v>6.7</v>
-      </c>
-      <c r="AL13" t="inlineStr">
-        <is>
-          <t>Fresh</t>
-        </is>
-      </c>
-      <c r="AM13" t="inlineStr">
-        <is>
-          <t>Confirmed Accumulation</t>
-        </is>
-      </c>
-      <c r="AN13" t="inlineStr">
-        <is>
-          <t>Confirmed Accumulation</t>
-        </is>
-      </c>
-      <c r="AO13" t="inlineStr">
-        <is>
-          <t>05-08-2026</t>
-        </is>
-      </c>
-      <c r="AP13" t="inlineStr">
-        <is>
-          <t>15-09-2026</t>
-        </is>
-      </c>
-      <c r="AQ13" t="n">
-        <v>41</v>
-      </c>
-      <c r="AR13" t="n">
-        <v>47</v>
-      </c>
-      <c r="AS13" t="n">
-        <v>6</v>
-      </c>
       <c r="AT13" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="AU13" t="n">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="AV13" t="n">
-        <v>5</v>
+        <v>16</v>
       </c>
       <c r="AW13" t="n">
-        <v>11</v>
+        <v>16</v>
       </c>
       <c r="AX13" t="n">
-        <v>11</v>
+        <v>16</v>
       </c>
       <c r="AY13" t="n">
-        <v>789002</v>
+        <v>10676672</v>
       </c>
       <c r="AZ13" t="n">
-        <v>1412746</v>
+        <v>20024685</v>
       </c>
       <c r="BA13" t="n">
-        <v>2942912</v>
+        <v>27987060</v>
       </c>
       <c r="BB13" t="n">
-        <v>19457263</v>
+        <v>27987060</v>
       </c>
       <c r="BC13" t="n">
-        <v>19457263</v>
+        <v>27987060</v>
       </c>
       <c r="BD13" t="n">
         <v>0</v>
@@ -3619,19 +3619,19 @@
         <v>0</v>
       </c>
       <c r="BN13" t="n">
-        <v>789002</v>
+        <v>10676672</v>
       </c>
       <c r="BO13" t="n">
-        <v>2942912</v>
+        <v>27987060</v>
       </c>
       <c r="BP13" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="BQ13" t="n">
         <v>0</v>
       </c>
       <c r="BR13" t="n">
-        <v>0.2681</v>
+        <v>0.3815</v>
       </c>
     </row>
     <row r="14">
@@ -3712,10 +3712,10 @@
         <v>0.151</v>
       </c>
       <c r="W14" t="n">
-        <v>733</v>
+        <v>736</v>
       </c>
       <c r="X14" t="n">
-        <v>61.2</v>
+        <v>61.5</v>
       </c>
       <c r="Y14" t="n">
         <v>3</v>
@@ -3941,10 +3941,10 @@
         </is>
       </c>
       <c r="V15" t="n">
-        <v>2.288</v>
+        <v>2.289</v>
       </c>
       <c r="W15" t="n">
-        <v>2604</v>
+        <v>2603</v>
       </c>
       <c r="X15" t="n">
         <v>204</v>
@@ -4173,13 +4173,13 @@
         </is>
       </c>
       <c r="V16" t="n">
-        <v>0.441</v>
+        <v>0.425</v>
       </c>
       <c r="W16" t="n">
-        <v>420</v>
+        <v>436</v>
       </c>
       <c r="X16" t="n">
-        <v>39</v>
+        <v>40.5</v>
       </c>
       <c r="Y16" t="n">
         <v>21</v>
@@ -4408,10 +4408,10 @@
         <v>0.077</v>
       </c>
       <c r="W17" t="n">
-        <v>439</v>
+        <v>437</v>
       </c>
       <c r="X17" t="n">
-        <v>13</v>
+        <v>12.9</v>
       </c>
       <c r="Y17" t="n">
         <v>-8</v>
@@ -4869,13 +4869,13 @@
         </is>
       </c>
       <c r="V19" t="n">
-        <v>0.282</v>
+        <v>0.275</v>
       </c>
       <c r="W19" t="n">
-        <v>199</v>
+        <v>204</v>
       </c>
       <c r="X19" t="n">
-        <v>24.8</v>
+        <v>25.4</v>
       </c>
       <c r="Y19" t="n">
         <v>12</v>
@@ -5101,13 +5101,13 @@
         </is>
       </c>
       <c r="V20" t="n">
-        <v>0.497</v>
+        <v>0.48</v>
       </c>
       <c r="W20" t="n">
-        <v>684</v>
+        <v>707</v>
       </c>
       <c r="X20" t="n">
-        <v>15.1</v>
+        <v>15.6</v>
       </c>
       <c r="Y20" t="n">
         <v>-1</v>
@@ -5333,13 +5333,13 @@
         </is>
       </c>
       <c r="V21" t="n">
-        <v>0.135</v>
+        <v>0.137</v>
       </c>
       <c r="W21" t="n">
-        <v>367</v>
+        <v>362</v>
       </c>
       <c r="X21" t="n">
-        <v>5.93</v>
+        <v>5.86</v>
       </c>
       <c r="Y21" t="n">
         <v>118</v>
@@ -5564,10 +5564,10 @@
         <v>0.007</v>
       </c>
       <c r="W22" t="n">
-        <v>5704</v>
+        <v>5657</v>
       </c>
       <c r="X22" t="n">
-        <v>9.640000000000001</v>
+        <v>9.550000000000001</v>
       </c>
       <c r="Y22" t="n">
         <v>43</v>
@@ -5793,13 +5793,13 @@
         </is>
       </c>
       <c r="V23" t="n">
-        <v>0.042</v>
+        <v>0.04</v>
       </c>
       <c r="W23" t="n">
-        <v>992</v>
+        <v>1036</v>
       </c>
       <c r="X23" t="n">
-        <v>106</v>
+        <v>111</v>
       </c>
       <c r="Y23" t="n">
         <v>15</v>
@@ -6025,13 +6025,13 @@
         </is>
       </c>
       <c r="V24" t="n">
-        <v>0.059</v>
+        <v>0.058</v>
       </c>
       <c r="W24" t="n">
-        <v>1855</v>
+        <v>1883</v>
       </c>
       <c r="X24" t="n">
-        <v>42.6</v>
+        <v>43.2</v>
       </c>
       <c r="Y24" t="n">
         <v>20</v>
@@ -6260,10 +6260,10 @@
         <v>0.038</v>
       </c>
       <c r="W25" t="n">
-        <v>3511</v>
+        <v>3571</v>
       </c>
       <c r="X25" t="n">
-        <v>20.8</v>
+        <v>21.2</v>
       </c>
       <c r="Y25" t="n">
         <v>-4</v>
@@ -6489,13 +6489,13 @@
         </is>
       </c>
       <c r="V26" t="n">
-        <v>0.096</v>
+        <v>0.094</v>
       </c>
       <c r="W26" t="n">
-        <v>1550</v>
+        <v>1571</v>
       </c>
       <c r="X26" t="n">
-        <v>14</v>
+        <v>14.2</v>
       </c>
       <c r="Y26" t="n">
         <v>6</v>
@@ -6724,10 +6724,10 @@
         <v>0.008999999999999999</v>
       </c>
       <c r="W27" t="n">
-        <v>53479</v>
+        <v>53170</v>
       </c>
       <c r="X27" t="n">
-        <v>45.3</v>
+        <v>45</v>
       </c>
       <c r="Y27" t="n">
         <v>5</v>
@@ -6956,10 +6956,10 @@
         <v>0.052</v>
       </c>
       <c r="W28" t="n">
-        <v>5072</v>
+        <v>5048</v>
       </c>
       <c r="X28" t="n">
-        <v>33</v>
+        <v>32.9</v>
       </c>
       <c r="Y28" t="n">
         <v>-25</v>
@@ -7185,13 +7185,13 @@
         </is>
       </c>
       <c r="V29" t="n">
-        <v>0.488</v>
+        <v>0.479</v>
       </c>
       <c r="W29" t="n">
-        <v>450</v>
+        <v>458</v>
       </c>
       <c r="X29" t="n">
-        <v>11.2</v>
+        <v>11.4</v>
       </c>
       <c r="Y29" t="n">
         <v>19</v>
@@ -7417,13 +7417,13 @@
         </is>
       </c>
       <c r="V30" t="n">
-        <v>0.667</v>
+        <v>0.646</v>
       </c>
       <c r="W30" t="n">
-        <v>352</v>
+        <v>363</v>
       </c>
       <c r="X30" t="n">
-        <v>1134</v>
+        <v>1172</v>
       </c>
       <c r="Y30" t="n">
         <v>-61</v>
@@ -7648,10 +7648,10 @@
         <v>0</v>
       </c>
       <c r="W31" t="n">
-        <v>3815</v>
+        <v>3731</v>
       </c>
       <c r="X31" t="n">
-        <v>85.90000000000001</v>
+        <v>84</v>
       </c>
       <c r="Y31" t="n">
         <v>42</v>
@@ -7880,7 +7880,7 @@
         <v>0.02</v>
       </c>
       <c r="W32" t="n">
-        <v>9615</v>
+        <v>9613</v>
       </c>
       <c r="X32" t="n">
         <v>12.7</v>
@@ -8112,10 +8112,10 @@
         <v>0.033</v>
       </c>
       <c r="W33" t="n">
-        <v>738</v>
+        <v>734</v>
       </c>
       <c r="X33" t="n">
-        <v>48.1</v>
+        <v>47.9</v>
       </c>
       <c r="Y33" t="n">
         <v>7</v>
@@ -8341,13 +8341,13 @@
         </is>
       </c>
       <c r="V34" t="n">
-        <v>0.535</v>
+        <v>0.539</v>
       </c>
       <c r="W34" t="n">
-        <v>3616</v>
+        <v>3586</v>
       </c>
       <c r="X34" t="n">
-        <v>25.3</v>
+        <v>25.1</v>
       </c>
       <c r="Y34" t="n">
         <v>2</v>
@@ -8579,7 +8579,7 @@
         <v>201</v>
       </c>
       <c r="X35" t="n">
-        <v>5.89</v>
+        <v>5.88</v>
       </c>
       <c r="Y35" t="n">
         <v>31</v>
@@ -8804,7 +8804,7 @@
         <v>0</v>
       </c>
       <c r="W36" t="n">
-        <v>485</v>
+        <v>487</v>
       </c>
       <c r="X36" t="n">
         <v>11.4</v>
@@ -9033,13 +9033,13 @@
         </is>
       </c>
       <c r="V37" t="n">
-        <v>0.209</v>
+        <v>0.21</v>
       </c>
       <c r="W37" t="n">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="X37" t="n">
-        <v>25.6</v>
+        <v>25.4</v>
       </c>
       <c r="Y37" t="n">
         <v>21</v>
@@ -9265,13 +9265,13 @@
         </is>
       </c>
       <c r="V38" t="n">
-        <v>0.126</v>
+        <v>0.127</v>
       </c>
       <c r="W38" t="n">
-        <v>590</v>
+        <v>586</v>
       </c>
       <c r="X38" t="n">
-        <v>14</v>
+        <v>13.9</v>
       </c>
       <c r="Y38" t="n">
         <v>61</v>
@@ -9498,7 +9498,7 @@
         <v>0.06900000000000001</v>
       </c>
       <c r="W39" t="n">
-        <v>814</v>
+        <v>815</v>
       </c>
       <c r="X39" t="n">
         <v>19.5</v>
@@ -9719,13 +9719,13 @@
         </is>
       </c>
       <c r="V40" t="n">
-        <v>0.074</v>
+        <v>0.075</v>
       </c>
       <c r="W40" t="n">
-        <v>728</v>
+        <v>721</v>
       </c>
       <c r="X40" t="n">
-        <v>13.2</v>
+        <v>13.1</v>
       </c>
       <c r="Y40" t="n">
         <v>185</v>
@@ -9949,13 +9949,13 @@
         </is>
       </c>
       <c r="V41" t="n">
-        <v>0.35</v>
+        <v>0.348</v>
       </c>
       <c r="W41" t="n">
-        <v>400</v>
+        <v>402</v>
       </c>
       <c r="X41" t="n">
-        <v>99.09999999999999</v>
+        <v>99.59999999999999</v>
       </c>
       <c r="Y41" t="n">
         <v>246</v>
@@ -10181,13 +10181,13 @@
         </is>
       </c>
       <c r="V42" t="n">
-        <v>0.221</v>
+        <v>0.223</v>
       </c>
       <c r="W42" t="n">
-        <v>1805</v>
+        <v>1790</v>
       </c>
       <c r="X42" t="n">
-        <v>19.1</v>
+        <v>18.9</v>
       </c>
       <c r="Y42" t="n">
         <v>-3</v>
@@ -10413,10 +10413,10 @@
         </is>
       </c>
       <c r="V43" t="n">
-        <v>0.027</v>
+        <v>0.026</v>
       </c>
       <c r="W43" t="n">
-        <v>916</v>
+        <v>942</v>
       </c>
       <c r="X43" t="inlineStr"/>
       <c r="Y43" t="n">
@@ -10646,10 +10646,10 @@
         <v>0.126</v>
       </c>
       <c r="W44" t="n">
-        <v>988</v>
+        <v>990</v>
       </c>
       <c r="X44" t="n">
-        <v>26.9</v>
+        <v>27</v>
       </c>
       <c r="Y44" t="n">
         <v>9</v>
@@ -10878,10 +10878,10 @@
         <v>0</v>
       </c>
       <c r="W45" t="n">
-        <v>9012</v>
+        <v>8944</v>
       </c>
       <c r="X45" t="n">
-        <v>15.3</v>
+        <v>15.2</v>
       </c>
       <c r="Y45" t="n">
         <v>21</v>
@@ -11339,13 +11339,13 @@
         </is>
       </c>
       <c r="V47" t="n">
-        <v>0.043</v>
+        <v>0.039</v>
       </c>
       <c r="W47" t="n">
-        <v>1602</v>
+        <v>1763</v>
       </c>
       <c r="X47" t="n">
-        <v>20.9</v>
+        <v>23</v>
       </c>
       <c r="Y47" t="n">
         <v>10</v>
@@ -11574,10 +11574,10 @@
         <v>0</v>
       </c>
       <c r="W48" t="n">
-        <v>2384</v>
+        <v>2353</v>
       </c>
       <c r="X48" t="n">
-        <v>705</v>
+        <v>696</v>
       </c>
       <c r="Y48" t="n">
         <v>3</v>
@@ -11803,13 +11803,13 @@
         </is>
       </c>
       <c r="V49" t="n">
-        <v>0.081</v>
+        <v>0.082</v>
       </c>
       <c r="W49" t="n">
-        <v>1692</v>
+        <v>1662</v>
       </c>
       <c r="X49" t="n">
-        <v>30.5</v>
+        <v>30</v>
       </c>
       <c r="Y49" t="n">
         <v>39</v>
@@ -12038,10 +12038,10 @@
         <v>0</v>
       </c>
       <c r="W50" t="n">
-        <v>114199</v>
+        <v>115943</v>
       </c>
       <c r="X50" t="n">
-        <v>32.9</v>
+        <v>33.4</v>
       </c>
       <c r="Y50" t="n">
         <v>18</v>
@@ -12512,175 +12512,175 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>SRHHYPOLTD</t>
+          <t>PKTEA</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Sree Rayalaseema Hi-Strength Hypo Limited</t>
+          <t>THE PERIA KARAMALAI TEA &amp; PRODUCE COMPANY LIMITED</t>
         </is>
       </c>
       <c r="C9" t="n">
-        <v>523.1</v>
+        <v>910</v>
       </c>
       <c r="D9" t="n">
-        <v>509.48</v>
+        <v>734.17</v>
       </c>
       <c r="E9" t="n">
-        <v>2.7</v>
+        <v>23.9</v>
       </c>
       <c r="F9" t="n">
-        <v>62.09</v>
+        <v>61.71</v>
       </c>
       <c r="G9" t="n">
-        <v>2.8</v>
+        <v>2.13</v>
       </c>
       <c r="H9" t="n">
-        <v>16</v>
+        <v>4</v>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>18-09-2026</t>
+          <t>04-09-2026</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>PKTEA</t>
+          <t>THANGAMAYL</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>THE PERIA KARAMALAI TEA &amp; PRODUCE COMPANY LIMITED</t>
+          <t>THANGAMAYIL JEWELLERY LIMITED</t>
         </is>
       </c>
       <c r="C10" t="n">
-        <v>910</v>
+        <v>5044.5</v>
       </c>
       <c r="D10" t="n">
-        <v>734.17</v>
+        <v>5198.76</v>
       </c>
       <c r="E10" t="n">
-        <v>23.9</v>
+        <v>-3</v>
       </c>
       <c r="F10" t="n">
-        <v>61.71</v>
+        <v>67.16</v>
       </c>
       <c r="G10" t="n">
-        <v>2.13</v>
+        <v>7.21</v>
       </c>
       <c r="H10" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>04-09-2026</t>
+          <t>31-08-2026</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>STEL</t>
+          <t>OBCL</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>STEL HOLDINGS LIMITED</t>
+          <t>OBCL LIMITED</t>
         </is>
       </c>
       <c r="C11" t="n">
-        <v>654.2</v>
+        <v>57.02</v>
       </c>
       <c r="D11" t="n">
-        <v>625.41</v>
+        <v>53.45</v>
       </c>
       <c r="E11" t="n">
-        <v>4.6</v>
+        <v>6.7</v>
       </c>
       <c r="F11" t="n">
-        <v>64.68000000000001</v>
+        <v>67.23</v>
       </c>
       <c r="G11" t="n">
-        <v>3.96</v>
+        <v>1.95</v>
       </c>
       <c r="H11" t="n">
-        <v>33</v>
+        <v>11</v>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>18-09-2026</t>
+          <t>15-09-2026</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>THANGAMAYL</t>
+          <t>STEL</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>THANGAMAYIL JEWELLERY LIMITED</t>
+          <t>STEL HOLDINGS LIMITED</t>
         </is>
       </c>
       <c r="C12" t="n">
-        <v>5044.5</v>
+        <v>654.2</v>
       </c>
       <c r="D12" t="n">
-        <v>5198.76</v>
+        <v>625.41</v>
       </c>
       <c r="E12" t="n">
-        <v>-3</v>
+        <v>4.6</v>
       </c>
       <c r="F12" t="n">
-        <v>67.16</v>
+        <v>64.68000000000001</v>
       </c>
       <c r="G12" t="n">
-        <v>7.21</v>
+        <v>3.96</v>
       </c>
       <c r="H12" t="n">
-        <v>6</v>
+        <v>33</v>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>31-08-2026</t>
+          <t>18-09-2026</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>OBCL</t>
+          <t>SRHHYPOLTD</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>OBCL LIMITED</t>
+          <t>Sree Rayalaseema Hi-Strength Hypo Limited</t>
         </is>
       </c>
       <c r="C13" t="n">
-        <v>57.02</v>
+        <v>523.1</v>
       </c>
       <c r="D13" t="n">
-        <v>53.45</v>
+        <v>509.48</v>
       </c>
       <c r="E13" t="n">
-        <v>6.7</v>
+        <v>2.7</v>
       </c>
       <c r="F13" t="n">
-        <v>67.23</v>
+        <v>62.09</v>
       </c>
       <c r="G13" t="n">
-        <v>1.95</v>
+        <v>2.8</v>
       </c>
       <c r="H13" t="n">
-        <v>11</v>
+        <v>16</v>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>15-09-2026</t>
+          <t>18-09-2026</t>
         </is>
       </c>
     </row>

--- a/output/2026-09-21/enriched_analysis.xlsx
+++ b/output/2026-09-21/enriched_analysis.xlsx
@@ -1396,7 +1396,7 @@
         <v>0.284</v>
       </c>
       <c r="W4" t="n">
-        <v>1077</v>
+        <v>1078</v>
       </c>
       <c r="X4" t="n">
         <v>10.6</v>
@@ -2783,13 +2783,13 @@
         </is>
       </c>
       <c r="V10" t="n">
-        <v>0.875</v>
+        <v>0.879</v>
       </c>
       <c r="W10" t="n">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="X10" t="n">
-        <v>9.01</v>
+        <v>8.960000000000001</v>
       </c>
       <c r="Y10" t="n">
         <v>17</v>
@@ -3712,10 +3712,10 @@
         <v>0.047</v>
       </c>
       <c r="W14" t="n">
-        <v>15367</v>
+        <v>15415</v>
       </c>
       <c r="X14" t="n">
-        <v>39.1</v>
+        <v>39.2</v>
       </c>
       <c r="Y14" t="n">
         <v>83</v>
@@ -4637,13 +4637,13 @@
         </is>
       </c>
       <c r="V18" t="n">
-        <v>0.433</v>
+        <v>0.432</v>
       </c>
       <c r="W18" t="n">
-        <v>428</v>
+        <v>429</v>
       </c>
       <c r="X18" t="n">
-        <v>39.7</v>
+        <v>39.8</v>
       </c>
       <c r="Y18" t="n">
         <v>21</v>
@@ -5101,13 +5101,13 @@
         </is>
       </c>
       <c r="V20" t="n">
-        <v>0.289</v>
+        <v>0.291</v>
       </c>
       <c r="W20" t="n">
-        <v>206</v>
+        <v>204</v>
       </c>
       <c r="X20" t="n">
-        <v>25.6</v>
+        <v>25.4</v>
       </c>
       <c r="Y20" t="n">
         <v>12</v>
@@ -8351,7 +8351,7 @@
         <v>10.7</v>
       </c>
       <c r="AD34" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AE34" t="b">
         <v>1</v>
@@ -9256,7 +9256,7 @@
         <v>0.021</v>
       </c>
       <c r="W38" t="n">
-        <v>9458</v>
+        <v>9484</v>
       </c>
       <c r="X38" t="n">
         <v>12.5</v>
@@ -9952,10 +9952,10 @@
         <v>0</v>
       </c>
       <c r="W41" t="n">
-        <v>485</v>
+        <v>484</v>
       </c>
       <c r="X41" t="n">
-        <v>11.4</v>
+        <v>11.3</v>
       </c>
       <c r="Y41" t="n">
         <v>5</v>
@@ -11806,10 +11806,10 @@
         <v>0</v>
       </c>
       <c r="W49" t="n">
-        <v>8944</v>
+        <v>8901</v>
       </c>
       <c r="X49" t="n">
-        <v>15.2</v>
+        <v>15.1</v>
       </c>
       <c r="Y49" t="n">
         <v>21</v>
